--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_17_48.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_17_48.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5646840.393971477</v>
+        <v>5686051.025647625</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6852621.339836506</v>
+        <v>6852621.33983651</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6852621.339836506</v>
+        <v>6852621.33983651</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2903760.589688157</v>
+        <v>2903760.589688156</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2903760.589688157</v>
+        <v>2903760.589688156</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36731577.73484947</v>
+        <v>36731577.73484946</v>
       </c>
     </row>
   </sheetData>
@@ -654,40 +654,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>481.9993129555745</v>
       </c>
       <c r="C2" t="n">
-        <v>49.47457824299391</v>
+        <v>449.4745782429939</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E2" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F2" t="n">
-        <v>404.8896287080119</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>408.0096587035274</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>419.7382696589336</v>
       </c>
       <c r="K2" t="n">
-        <v>774.3370345097345</v>
+        <v>66.13418277953816</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>815</v>
+        <v>298.9910820919849</v>
       </c>
       <c r="N2" t="n">
         <v>815</v>
@@ -696,19 +696,19 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="Q2" t="n">
-        <v>371.9706110579117</v>
+        <v>781.1823806961576</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>97.4501913854146</v>
       </c>
       <c r="S2" t="n">
-        <v>191.3386006767583</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
-        <v>586.6755817285639</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
@@ -778,25 +778,25 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>547.2737972923793</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S3" t="n">
         <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
-        <v>5.357765217513816</v>
+        <v>63.08338960093648</v>
       </c>
       <c r="U3" t="n">
         <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
-        <v>299.1570264844632</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815778182</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>178.4897458300101</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>49.47457824299391</v>
+        <v>449.4745782429939</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>106.8295886142851</v>
       </c>
       <c r="E5" t="n">
         <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
-        <v>404.8896287080119</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>403.7573722870162</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
         <v>408.0096587035274</v>
@@ -918,22 +918,22 @@
         <v>419.7382696589336</v>
       </c>
       <c r="K5" t="n">
-        <v>66.13418277953816</v>
+        <v>815</v>
       </c>
       <c r="L5" t="n">
-        <v>213.6262340571984</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>298.9910820919849</v>
+        <v>815</v>
       </c>
       <c r="N5" t="n">
-        <v>195.5855355810472</v>
+        <v>774.3370345098391</v>
       </c>
       <c r="O5" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>371.9706110579117</v>
@@ -942,7 +942,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
@@ -973,13 +973,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>167.1158402638074</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>387.8730357844536</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>466.5639999646113</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
         <v>5.357765217513816</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>23.54762815777917</v>
+        <v>23.54762815779074</v>
       </c>
       <c r="M7" t="n">
         <v>120.6316114025499</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.99931295557451</v>
+        <v>481.9993129555745</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1143,22 +1143,22 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>403.7573722870162</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>408.0096587035274</v>
+        <v>104.5000915779627</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
-        <v>419.7382696589336</v>
+        <v>798.7814999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>783.0093003029165</v>
+        <v>66.13418277957176</v>
       </c>
       <c r="L8" t="n">
-        <v>815</v>
+        <v>649.5830037161319</v>
       </c>
       <c r="M8" t="n">
         <v>298.9910820919849</v>
@@ -1167,22 +1167,22 @@
         <v>195.5855355810472</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="P8" t="n">
-        <v>311.7511165340938</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>371.9706110579117</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>442.2171995050529</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
-        <v>586.6755817285639</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U8" t="n">
         <v>249.2212965486107</v>
@@ -1194,10 +1194,10 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>192.2818334606677</v>
+        <v>592.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>111.3174326828064</v>
+        <v>511.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1264,19 +1264,19 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>110.6069044797725</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>77.58836382881024</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815780607</v>
+        <v>23.54762815778182</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1374,7 +1374,7 @@
         <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>30.92440624890541</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
         <v>269.8481678023229</v>
@@ -1422,7 +1422,7 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>5.045807420610877</v>
       </c>
       <c r="V11" t="n">
         <v>404.8510241668239</v>
@@ -1611,13 +1611,13 @@
         <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>153.8896287080119</v>
+        <v>71.46048198731131</v>
       </c>
       <c r="G14" t="n">
-        <v>152.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>157.0096587035274</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>234.1493833545609</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T14" t="n">
         <v>335.6755817285639</v>
@@ -1662,7 +1662,7 @@
         <v>398.2212965486107</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W14" t="n">
         <v>387.3734759809475</v>
@@ -1790,13 +1790,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>172.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>269.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>49.93595474591673</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -1805,10 +1805,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>52.97841917455702</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>36.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1860,7 +1860,7 @@
         <v>129.0096587035274</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.450191385413969</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.450191385414405</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>215.8481678023229</v>
@@ -2042,13 +2042,13 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>338.6387678008247</v>
+        <v>246.7999352485069</v>
       </c>
       <c r="R19" t="n">
         <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>8.465352849462363</v>
       </c>
     </row>
     <row r="20">
@@ -2234,13 +2234,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>210.1299990538228</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>377.7929984536983</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2325,7 +2325,7 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F23" t="n">
-        <v>125.8896287080119</v>
+        <v>129.3398200934258</v>
       </c>
       <c r="G23" t="n">
         <v>124.7573722870162</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>219.2983591877372</v>
+        <v>215.8481678023229</v>
       </c>
       <c r="T23" t="n">
         <v>307.6755817285639</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>446.839266425598</v>
+        <v>375.8120936167418</v>
       </c>
       <c r="R25" t="n">
-        <v>339.4016293563778</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2553,22 +2553,22 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>131.199675845388</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2610,13 +2610,13 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
-        <v>185.8723261655594</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>413.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
         <v>286.3174326828064</v>
@@ -2741,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>45.14518808597776</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2787,22 +2787,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>179.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>424.2212965486107</v>
+        <v>197.3003105001137</v>
       </c>
       <c r="V29" t="n">
         <v>404.8510241668239</v>
@@ -2856,7 +2856,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>129.9243474290386</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -2945,16 +2945,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2978,10 +2978,10 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>50.28912402630603</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>29.51163133132237</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3008,13 +3008,13 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3033,22 +3033,22 @@
         <v>126.3391557398498</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>120.3632896068686</v>
       </c>
       <c r="F32" t="n">
-        <v>120.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>119.7573722870162</v>
       </c>
       <c r="H32" t="n">
-        <v>96.61753969581041</v>
+        <v>97.14387879695363</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>742.9157999999999</v>
+        <v>362.7382696589336</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3060,13 +3060,13 @@
         <v>241.9910820919849</v>
       </c>
       <c r="N32" t="n">
-        <v>75.49467550643637</v>
+        <v>138.5855355810472</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>317.0866702663771</v>
       </c>
       <c r="Q32" t="n">
         <v>314.9706110579117</v>
@@ -3218,16 +3218,16 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>287.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>356.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>199.4747716005747</v>
+        <v>403.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>439.6575136229972</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3288,25 +3288,25 @@
         <v>362.7382696589336</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>758</v>
       </c>
       <c r="L35" t="n">
-        <v>551.7865359278883</v>
+        <v>758</v>
       </c>
       <c r="M35" t="n">
-        <v>758.0000000000006</v>
+        <v>241.9910820919849</v>
       </c>
       <c r="N35" t="n">
-        <v>343.823080960479</v>
+        <v>138.5855355810472</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>184.9781881574513</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>742.915800000012</v>
+        <v>314.9706110579117</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>300.6755817285639</v>
       </c>
       <c r="U35" t="n">
-        <v>243.4658879340254</v>
+        <v>363.2212965486107</v>
       </c>
       <c r="V35" t="n">
         <v>343.8510241668239</v>
@@ -3327,7 +3327,7 @@
         <v>352.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>306.2818334606677</v>
+        <v>186.5264248460823</v>
       </c>
       <c r="Y35" t="n">
         <v>225.3174326828064</v>
@@ -3446,13 +3446,13 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2.520773801143037</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>137.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>234.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3461,13 +3461,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>401.4478973282775</v>
       </c>
       <c r="Q37" t="n">
-        <v>439.839266425598</v>
+        <v>25.03233832559617</v>
       </c>
       <c r="R37" t="n">
-        <v>51.07773099849231</v>
+        <v>440.6021279811511</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3501,13 +3501,13 @@
         <v>195.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>43.71916962840848</v>
+        <v>163.4745782429939</v>
       </c>
       <c r="D38" t="n">
         <v>124.3391557398498</v>
       </c>
       <c r="E38" t="n">
-        <v>118.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>118.8896287080119</v>
@@ -3516,7 +3516,7 @@
         <v>117.7573722870162</v>
       </c>
       <c r="H38" t="n">
-        <v>122.0096587035274</v>
+        <v>120.6175396958106</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3525,22 +3525,22 @@
         <v>362.7382696589336</v>
       </c>
       <c r="K38" t="n">
-        <v>432.3165347064471</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>510.6616534510117</v>
+        <v>551.7865359278771</v>
       </c>
       <c r="M38" t="n">
         <v>241.9910820919849</v>
       </c>
       <c r="N38" t="n">
-        <v>138.5855355810472</v>
+        <v>758</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>529.7771878105943</v>
       </c>
       <c r="P38" t="n">
-        <v>758</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>314.9706110579117</v>
@@ -3701,13 +3701,13 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>350.1067559510183</v>
+        <v>439.839266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>440.6021279811511</v>
+        <v>427.2430972094267</v>
       </c>
       <c r="S40" t="n">
-        <v>76.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3735,13 +3735,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>257.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>225.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>186.3391557398498</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>154.7244105579681</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>26.87859882829446</v>
+        <v>24.58197337364512</v>
       </c>
       <c r="S41" t="n">
         <v>270.8481678023229</v>
@@ -3804,7 +3804,7 @@
         <v>368.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>287.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3905,10 +3905,10 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>50.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>21.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>4.77112610161862</v>
@@ -3920,10 +3920,10 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>64.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>167.1728901847974</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>303.1203927952346</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3975,22 +3975,22 @@
         <v>283.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>251.4745782429939</v>
       </c>
       <c r="D44" t="n">
         <v>212.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>206.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>206.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>210.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,16 +4023,16 @@
         <v>52.87859882829446</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>296.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>189.3429891666278</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>451.2212965486107</v>
       </c>
       <c r="V44" t="n">
-        <v>431.8510241668239</v>
+        <v>244.9125477579319</v>
       </c>
       <c r="W44" t="n">
         <v>440.3734759809475</v>
@@ -4057,7 +4057,7 @@
         <v>163.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>149.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>144.6720972219126</v>
@@ -4066,7 +4066,7 @@
         <v>141.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>127.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>134.1680871864211</v>
@@ -4099,16 +4099,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>99.55902976902487</v>
+        <v>349.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>268.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>207.3577652175138</v>
       </c>
       <c r="U45" t="n">
-        <v>202.2103597601867</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>216.5106671915202</v>
@@ -4117,7 +4117,7 @@
         <v>234.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>221.8627394453875</v>
+        <v>142.5250567566764</v>
       </c>
       <c r="Y45" t="n">
         <v>201.3913927661343</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>30.77112610161862</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4184,16 +4184,16 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>12.02456650625771</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.170310216216194</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>28.37280983870968</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1106.528124213083</v>
+        <v>1358.971397260877</v>
       </c>
       <c r="C2" t="n">
-        <v>1056.553802755514</v>
+        <v>904.9566717629029</v>
       </c>
       <c r="D2" t="n">
-        <v>1046.1102110991</v>
+        <v>490.472676066085</v>
       </c>
       <c r="E2" t="n">
-        <v>1041.702847859839</v>
+        <v>82.02490878641969</v>
       </c>
       <c r="F2" t="n">
-        <v>632.7234249224528</v>
+        <v>77.08588988943801</v>
       </c>
       <c r="G2" t="n">
-        <v>628.9280993800121</v>
+        <v>73.29056434699739</v>
       </c>
       <c r="H2" t="n">
-        <v>216.7971309926107</v>
+        <v>65.2</v>
       </c>
       <c r="I2" t="n">
         <v>65.2</v>
@@ -4324,49 +4324,49 @@
         <v>448.0719498394611</v>
       </c>
       <c r="K2" t="n">
-        <v>472.7633291225574</v>
+        <v>1156.448952311256</v>
       </c>
       <c r="L2" t="n">
-        <v>1247.942536422134</v>
+        <v>1963.298952311256</v>
       </c>
       <c r="M2" t="n">
-        <v>1231.56021318981</v>
+        <v>2468.137758278948</v>
       </c>
       <c r="N2" t="n">
-        <v>1215.177889957487</v>
+        <v>2451.755435046624</v>
       </c>
       <c r="O2" t="n">
-        <v>2022.027889957487</v>
+        <v>3258.605435046624</v>
       </c>
       <c r="P2" t="n">
-        <v>2828.877889957487</v>
+        <v>3242.223111814301</v>
       </c>
       <c r="Q2" t="n">
         <v>3260</v>
       </c>
       <c r="R2" t="n">
-        <v>3006.587273910814</v>
+        <v>3161.565463247056</v>
       </c>
       <c r="S2" t="n">
-        <v>2813.315960095906</v>
+        <v>3065.759233143699</v>
       </c>
       <c r="T2" t="n">
-        <v>2220.714362390286</v>
+        <v>2877.198039478483</v>
       </c>
       <c r="U2" t="n">
-        <v>1968.975679007851</v>
+        <v>2625.459356096048</v>
       </c>
       <c r="V2" t="n">
-        <v>1736.802927324191</v>
+        <v>2393.286604412388</v>
       </c>
       <c r="W2" t="n">
-        <v>1496.021638454547</v>
+        <v>2152.505315542744</v>
       </c>
       <c r="X2" t="n">
-        <v>1301.797564251852</v>
+        <v>1958.281241340049</v>
       </c>
       <c r="Y2" t="n">
-        <v>1189.355713057098</v>
+        <v>1845.839390145295</v>
       </c>
     </row>
     <row r="3">
@@ -4421,22 +4421,22 @@
         <v>1220.632420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1045.804879873102</v>
+        <v>1220.632420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>493.0030644262537</v>
+        <v>1071.871008962092</v>
       </c>
       <c r="S3" t="n">
-        <v>425.7667008256362</v>
+        <v>1004.634645361474</v>
       </c>
       <c r="T3" t="n">
-        <v>420.3548167675414</v>
+        <v>940.9140498049728</v>
       </c>
       <c r="U3" t="n">
-        <v>420.1423321612922</v>
+        <v>940.7015651987235</v>
       </c>
       <c r="V3" t="n">
-        <v>117.9635175305213</v>
+        <v>522.0039215709254</v>
       </c>
       <c r="W3" t="n">
         <v>85.26337317715914</v>
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>460.7587853987519</v>
+        <v>462.4168525126554</v>
       </c>
       <c r="C4" t="n">
-        <v>586.7607912171876</v>
+        <v>462.4168525126554</v>
       </c>
       <c r="D4" t="n">
-        <v>700.0799353421877</v>
+        <v>575.7359966376555</v>
       </c>
       <c r="E4" t="n">
-        <v>817.9088395536007</v>
+        <v>575.7359966376555</v>
       </c>
       <c r="F4" t="n">
-        <v>942.2698121455362</v>
+        <v>575.7359966376555</v>
       </c>
       <c r="G4" t="n">
-        <v>1095.676378032422</v>
+        <v>713.9096043920238</v>
       </c>
       <c r="H4" t="n">
-        <v>1265.192963191819</v>
+        <v>883.4261895514213</v>
       </c>
       <c r="I4" t="n">
-        <v>1486.325842127902</v>
+        <v>1104.559068487504</v>
       </c>
       <c r="J4" t="n">
-        <v>1486.325842127902</v>
+        <v>1465.642809139955</v>
       </c>
       <c r="K4" t="n">
-        <v>1576.007243076827</v>
+        <v>1576.007243076824</v>
       </c>
       <c r="L4" t="n">
         <v>1552.221760089168</v>
@@ -4509,22 +4509,22 @@
         <v>102.4502550941731</v>
       </c>
       <c r="T4" t="n">
-        <v>102.4502550941731</v>
+        <v>290.525934252978</v>
       </c>
       <c r="U4" t="n">
-        <v>349.0014477324597</v>
+        <v>290.525934252978</v>
       </c>
       <c r="V4" t="n">
-        <v>349.0014477324597</v>
+        <v>290.525934252978</v>
       </c>
       <c r="W4" t="n">
-        <v>349.0014477324597</v>
+        <v>462.4168525126554</v>
       </c>
       <c r="X4" t="n">
-        <v>349.0014477324597</v>
+        <v>462.4168525126554</v>
       </c>
       <c r="Y4" t="n">
-        <v>349.0014477324597</v>
+        <v>462.4168525126554</v>
       </c>
     </row>
     <row r="5">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1510.568528253487</v>
+        <v>1203.993207924634</v>
       </c>
       <c r="C5" t="n">
-        <v>1460.594206795917</v>
+        <v>749.9784824266604</v>
       </c>
       <c r="D5" t="n">
-        <v>1450.150615139504</v>
+        <v>642.0698070586957</v>
       </c>
       <c r="E5" t="n">
-        <v>1445.743251900242</v>
+        <v>637.6624438194344</v>
       </c>
       <c r="F5" t="n">
-        <v>1036.763828962857</v>
+        <v>632.7234249224528</v>
       </c>
       <c r="G5" t="n">
         <v>628.9280993800121</v>
@@ -4561,19 +4561,19 @@
         <v>448.0719498394611</v>
       </c>
       <c r="K5" t="n">
-        <v>1156.448952311256</v>
+        <v>431.6896266071377</v>
       </c>
       <c r="L5" t="n">
-        <v>1747.514877506005</v>
+        <v>1206.868833906819</v>
       </c>
       <c r="M5" t="n">
-        <v>2252.353683473696</v>
+        <v>1190.486510674496</v>
       </c>
       <c r="N5" t="n">
-        <v>2861.642536422134</v>
+        <v>1215.177889957487</v>
       </c>
       <c r="O5" t="n">
-        <v>2845.26021318981</v>
+        <v>2022.027889957487</v>
       </c>
       <c r="P5" t="n">
         <v>2828.877889957487</v>
@@ -4585,25 +4585,25 @@
         <v>3006.587273910814</v>
       </c>
       <c r="S5" t="n">
-        <v>2910.781043807457</v>
+        <v>2506.740639767053</v>
       </c>
       <c r="T5" t="n">
-        <v>2722.219850142241</v>
+        <v>2318.179446101837</v>
       </c>
       <c r="U5" t="n">
-        <v>2470.481166759806</v>
+        <v>2066.440762719402</v>
       </c>
       <c r="V5" t="n">
-        <v>2238.308415076146</v>
+        <v>1834.268011035741</v>
       </c>
       <c r="W5" t="n">
-        <v>1997.527126206502</v>
+        <v>1593.486722166097</v>
       </c>
       <c r="X5" t="n">
-        <v>1803.303052003807</v>
+        <v>1399.262647963403</v>
       </c>
       <c r="Y5" t="n">
-        <v>1690.861200809053</v>
+        <v>1286.820796768649</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>284.5195817084329</v>
+        <v>931.5895195792149</v>
       </c>
       <c r="C6" t="n">
-        <v>284.5195817084329</v>
+        <v>762.785640524864</v>
       </c>
       <c r="D6" t="n">
-        <v>284.5195817084329</v>
+        <v>411.3334315372855</v>
       </c>
       <c r="E6" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="F6" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="G6" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="H6" t="n">
-        <v>284.5195817084329</v>
+        <v>65.2</v>
       </c>
       <c r="I6" t="n">
         <v>65.2</v>
@@ -4661,28 +4661,28 @@
         <v>1220.632420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>828.8414751317138</v>
+        <v>1071.871008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>357.5647074906922</v>
+        <v>1004.634645361474</v>
       </c>
       <c r="T6" t="n">
-        <v>352.1528234325975</v>
+        <v>999.2227613033796</v>
       </c>
       <c r="U6" t="n">
-        <v>351.9403388263482</v>
+        <v>999.0102766971303</v>
       </c>
       <c r="V6" t="n">
-        <v>337.2830992389542</v>
+        <v>984.3530371097362</v>
       </c>
       <c r="W6" t="n">
-        <v>304.582954885592</v>
+        <v>951.6528927563741</v>
       </c>
       <c r="X6" t="n">
-        <v>284.5195817084329</v>
+        <v>931.5895195792149</v>
       </c>
       <c r="Y6" t="n">
-        <v>284.5195817084329</v>
+        <v>931.5895195792149</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>553.3140629434636</v>
+        <v>176.9573376662921</v>
       </c>
       <c r="C7" t="n">
-        <v>553.3140629434636</v>
+        <v>302.9593434847279</v>
       </c>
       <c r="D7" t="n">
-        <v>666.6332070684637</v>
+        <v>318.3131617018017</v>
       </c>
       <c r="E7" t="n">
-        <v>784.4621112798767</v>
+        <v>436.1420659132147</v>
       </c>
       <c r="F7" t="n">
-        <v>908.8230838718122</v>
+        <v>560.5030385051501</v>
       </c>
       <c r="G7" t="n">
-        <v>1062.229649758697</v>
+        <v>713.9096043920354</v>
       </c>
       <c r="H7" t="n">
-        <v>1062.229649758697</v>
+        <v>883.4261895514329</v>
       </c>
       <c r="I7" t="n">
-        <v>1104.559068487504</v>
+        <v>1104.559068487516</v>
       </c>
       <c r="J7" t="n">
-        <v>1465.642809139955</v>
+        <v>1465.642809139967</v>
       </c>
       <c r="K7" t="n">
-        <v>1576.007243076824</v>
+        <v>1576.007243076835</v>
       </c>
       <c r="L7" t="n">
         <v>1552.221760089168</v>
@@ -4743,25 +4743,25 @@
         <v>65.2</v>
       </c>
       <c r="S7" t="n">
-        <v>102.4502550941731</v>
+        <v>65.2</v>
       </c>
       <c r="T7" t="n">
-        <v>290.525934252978</v>
+        <v>65.2</v>
       </c>
       <c r="U7" t="n">
-        <v>290.525934252978</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="n">
-        <v>290.525934252978</v>
+        <v>65.2</v>
       </c>
       <c r="W7" t="n">
-        <v>290.525934252978</v>
+        <v>65.2</v>
       </c>
       <c r="X7" t="n">
-        <v>441.5567252771715</v>
+        <v>65.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>441.5567252771715</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1106.528124213083</v>
+        <v>395.9123998438259</v>
       </c>
       <c r="C8" t="n">
-        <v>1056.553802755514</v>
+        <v>345.9380783862563</v>
       </c>
       <c r="D8" t="n">
-        <v>1046.1102110991</v>
+        <v>335.4944867298424</v>
       </c>
       <c r="E8" t="n">
-        <v>1041.702847859838</v>
+        <v>331.0871234905812</v>
       </c>
       <c r="F8" t="n">
-        <v>1036.763828962857</v>
+        <v>326.1481045935995</v>
       </c>
       <c r="G8" t="n">
-        <v>628.9280993800121</v>
+        <v>322.3527790511589</v>
       </c>
       <c r="H8" t="n">
         <v>216.7971309926107</v>
@@ -4795,22 +4795,22 @@
         <v>65.2</v>
       </c>
       <c r="J8" t="n">
-        <v>448.0719498394611</v>
+        <v>65.2</v>
       </c>
       <c r="K8" t="n">
-        <v>432.3326719848872</v>
+        <v>773.5770024717942</v>
       </c>
       <c r="L8" t="n">
-        <v>415.9503487525637</v>
+        <v>924.2825542736812</v>
       </c>
       <c r="M8" t="n">
-        <v>920.7891547202557</v>
+        <v>1429.121360241373</v>
       </c>
       <c r="N8" t="n">
-        <v>1530.078007668693</v>
+        <v>2038.41021318981</v>
       </c>
       <c r="O8" t="n">
-        <v>2336.928007668693</v>
+        <v>2022.027889957487</v>
       </c>
       <c r="P8" t="n">
         <v>2828.877889957487</v>
@@ -4819,28 +4819,28 @@
         <v>3260</v>
       </c>
       <c r="R8" t="n">
-        <v>3260</v>
+        <v>3006.587273910814</v>
       </c>
       <c r="S8" t="n">
-        <v>2813.315960095906</v>
+        <v>2910.781043807457</v>
       </c>
       <c r="T8" t="n">
-        <v>2220.714362390286</v>
+        <v>2722.219850142241</v>
       </c>
       <c r="U8" t="n">
-        <v>1968.975679007851</v>
+        <v>2470.481166759806</v>
       </c>
       <c r="V8" t="n">
-        <v>1736.80292732419</v>
+        <v>2238.308415076146</v>
       </c>
       <c r="W8" t="n">
-        <v>1496.021638454547</v>
+        <v>1997.527126206502</v>
       </c>
       <c r="X8" t="n">
-        <v>1301.797564251852</v>
+        <v>1399.262647963403</v>
       </c>
       <c r="Y8" t="n">
-        <v>1189.355713057098</v>
+        <v>882.7803927282447</v>
       </c>
     </row>
     <row r="9">
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>416.6522089875784</v>
+        <v>65.2</v>
       </c>
       <c r="C9" t="n">
-        <v>416.6522089875784</v>
+        <v>65.2</v>
       </c>
       <c r="D9" t="n">
         <v>65.2</v>
@@ -4907,19 +4907,19 @@
         <v>999.2227613033796</v>
       </c>
       <c r="U9" t="n">
-        <v>887.4986153642154</v>
+        <v>594.9698726567262</v>
       </c>
       <c r="V9" t="n">
-        <v>872.8413757768213</v>
+        <v>176.2722290289281</v>
       </c>
       <c r="W9" t="n">
-        <v>840.1412314234592</v>
+        <v>143.5720846755659</v>
       </c>
       <c r="X9" t="n">
-        <v>820.0778582463</v>
+        <v>65.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>416.6522089875784</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>442.6741342937526</v>
+        <v>698.8536316425992</v>
       </c>
       <c r="C10" t="n">
-        <v>442.6741342937526</v>
+        <v>698.8536316425992</v>
       </c>
       <c r="D10" t="n">
-        <v>442.6741342937526</v>
+        <v>698.8536316425992</v>
       </c>
       <c r="E10" t="n">
-        <v>560.5030385051657</v>
+        <v>816.6825358540123</v>
       </c>
       <c r="F10" t="n">
-        <v>560.5030385051657</v>
+        <v>816.6825358540123</v>
       </c>
       <c r="G10" t="n">
-        <v>713.9096043920509</v>
+        <v>816.6825358540123</v>
       </c>
       <c r="H10" t="n">
-        <v>883.4261895514485</v>
+        <v>986.1991210134098</v>
       </c>
       <c r="I10" t="n">
-        <v>1104.559068487531</v>
+        <v>1207.331999949493</v>
       </c>
       <c r="J10" t="n">
-        <v>1465.642809139983</v>
+        <v>1568.415740601944</v>
       </c>
       <c r="K10" t="n">
-        <v>1576.007243076851</v>
+        <v>1576.007243076827</v>
       </c>
       <c r="L10" t="n">
         <v>1552.221760089168</v>
@@ -4983,22 +4983,22 @@
         <v>102.4502550941731</v>
       </c>
       <c r="T10" t="n">
-        <v>290.525934252978</v>
+        <v>102.4502550941731</v>
       </c>
       <c r="U10" t="n">
-        <v>290.525934252978</v>
+        <v>349.0014477324597</v>
       </c>
       <c r="V10" t="n">
-        <v>290.525934252978</v>
+        <v>547.8228406184057</v>
       </c>
       <c r="W10" t="n">
-        <v>290.525934252978</v>
+        <v>547.8228406184057</v>
       </c>
       <c r="X10" t="n">
-        <v>441.5567252771715</v>
+        <v>698.8536316425992</v>
       </c>
       <c r="Y10" t="n">
-        <v>441.5567252771715</v>
+        <v>698.8536316425992</v>
       </c>
     </row>
     <row r="11">
@@ -5008,13 +5008,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>875.8112840629219</v>
+        <v>844.5745100741287</v>
       </c>
       <c r="C11" t="n">
-        <v>649.0692858376756</v>
+        <v>617.8325118488823</v>
       </c>
       <c r="D11" t="n">
-        <v>461.8580174135849</v>
+        <v>430.6212434247915</v>
       </c>
       <c r="E11" t="n">
         <v>430.6212434247915</v>
@@ -5032,19 +5032,19 @@
         <v>65.2</v>
       </c>
       <c r="J11" t="n">
-        <v>456.5091130376557</v>
+        <v>83.63175644363456</v>
       </c>
       <c r="K11" t="n">
-        <v>890.4817564436344</v>
+        <v>83.63175644363456</v>
       </c>
       <c r="L11" t="n">
-        <v>1697.331756443634</v>
+        <v>890.4817564436345</v>
       </c>
       <c r="M11" t="n">
-        <v>2208.180585172569</v>
+        <v>1401.330585172569</v>
       </c>
       <c r="N11" t="n">
-        <v>2821.400904947332</v>
+        <v>2014.550904947333</v>
       </c>
       <c r="O11" t="n">
         <v>2821.400904947332</v>
@@ -5056,28 +5056,28 @@
         <v>3260</v>
       </c>
       <c r="R11" t="n">
-        <v>3260</v>
+        <v>3233.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>2987.426093128967</v>
+        <v>2961.286094312508</v>
       </c>
       <c r="T11" t="n">
-        <v>2622.097222696074</v>
+        <v>2595.957223879615</v>
       </c>
       <c r="U11" t="n">
-        <v>2622.097222696074</v>
+        <v>2590.860448707281</v>
       </c>
       <c r="V11" t="n">
-        <v>2213.156794244736</v>
+        <v>2181.920020255943</v>
       </c>
       <c r="W11" t="n">
-        <v>1795.607828607416</v>
+        <v>1764.371054618622</v>
       </c>
       <c r="X11" t="n">
-        <v>1424.616077637044</v>
+        <v>1393.379303648251</v>
       </c>
       <c r="Y11" t="n">
-        <v>1135.406549674613</v>
+        <v>1104.16977568582</v>
       </c>
     </row>
     <row r="12">
@@ -5111,10 +5111,10 @@
         <v>72.99487796756496</v>
       </c>
       <c r="J12" t="n">
-        <v>419.7013981428639</v>
+        <v>215.8771006891148</v>
       </c>
       <c r="K12" t="n">
-        <v>831.6442142372473</v>
+        <v>627.8199167834982</v>
       </c>
       <c r="L12" t="n">
         <v>1121.920378378698</v>
@@ -5245,19 +5245,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1049.880488169968</v>
+        <v>657.4059340138207</v>
       </c>
       <c r="C14" t="n">
-        <v>849.4011162073475</v>
+        <v>456.9265620512006</v>
       </c>
       <c r="D14" t="n">
-        <v>688.452474045883</v>
+        <v>295.9779198897361</v>
       </c>
       <c r="E14" t="n">
-        <v>533.5400603015712</v>
+        <v>295.9779198897361</v>
       </c>
       <c r="F14" t="n">
-        <v>378.0959908995391</v>
+        <v>223.7956148520479</v>
       </c>
       <c r="G14" t="n">
         <v>223.7956148520479</v>
@@ -5269,19 +5269,19 @@
         <v>65.2</v>
       </c>
       <c r="J14" t="n">
-        <v>180.775390095766</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>890.4817564436344</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="L14" t="n">
-        <v>1697.331756443634</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="M14" t="n">
-        <v>2208.180585172569</v>
+        <v>1677.064308114459</v>
       </c>
       <c r="N14" t="n">
-        <v>2821.400904947332</v>
+        <v>2290.284627889223</v>
       </c>
       <c r="O14" t="n">
         <v>2821.400904947332</v>
@@ -5296,25 +5296,25 @@
         <v>3260</v>
       </c>
       <c r="S14" t="n">
-        <v>3023.485471359029</v>
+        <v>3013.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>2684.419227188763</v>
+        <v>2674.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>2282.175493301277</v>
+        <v>2272.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>2282.175493301277</v>
+        <v>1889.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>1890.889153926582</v>
+        <v>1498.414599770435</v>
       </c>
       <c r="X14" t="n">
-        <v>1546.160029218837</v>
+        <v>1153.68547506269</v>
       </c>
       <c r="Y14" t="n">
-        <v>1283.213127519033</v>
+        <v>890.7385733628859</v>
       </c>
     </row>
     <row r="15">
@@ -5348,13 +5348,13 @@
         <v>98.73487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>471.1813981428639</v>
+        <v>222.6913981428639</v>
       </c>
       <c r="K15" t="n">
-        <v>908.8642142372473</v>
+        <v>411.8842142372473</v>
       </c>
       <c r="L15" t="n">
-        <v>1180.214675832447</v>
+        <v>931.7246758324475</v>
       </c>
       <c r="M15" t="n">
         <v>1266.295217575307</v>
@@ -5363,7 +5363,7 @@
         <v>1399.575502182875</v>
       </c>
       <c r="O15" t="n">
-        <v>1887.107953866594</v>
+        <v>1803.15426247345</v>
       </c>
       <c r="P15" t="n">
         <v>2164.173606942957</v>
@@ -5403,52 +5403,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>247.1862842199767</v>
+        <v>284.0199739669084</v>
       </c>
       <c r="C16" t="n">
-        <v>247.1862842199767</v>
+        <v>284.0199739669084</v>
       </c>
       <c r="D16" t="n">
-        <v>247.1862842199767</v>
+        <v>284.0199739669084</v>
       </c>
       <c r="E16" t="n">
-        <v>247.1862842199767</v>
+        <v>284.0199739669084</v>
       </c>
       <c r="F16" t="n">
-        <v>247.1862842199767</v>
+        <v>284.0199739669084</v>
       </c>
       <c r="G16" t="n">
-        <v>253.082850106862</v>
+        <v>289.9165398537936</v>
       </c>
       <c r="H16" t="n">
-        <v>275.0894352662596</v>
+        <v>311.9231250131912</v>
       </c>
       <c r="I16" t="n">
-        <v>348.7123142023424</v>
+        <v>385.5460039492741</v>
       </c>
       <c r="J16" t="n">
-        <v>562.2860548547937</v>
+        <v>599.1197446017254</v>
       </c>
       <c r="K16" t="n">
-        <v>562.2860548547937</v>
+        <v>599.1197446017254</v>
       </c>
       <c r="L16" t="n">
-        <v>387.9955213620875</v>
+        <v>599.1197446017254</v>
       </c>
       <c r="M16" t="n">
-        <v>115.6403583292088</v>
+        <v>599.1197446017254</v>
       </c>
       <c r="N16" t="n">
-        <v>65.2</v>
+        <v>599.1197446017254</v>
       </c>
       <c r="O16" t="n">
-        <v>65.2</v>
+        <v>599.1197446017254</v>
       </c>
       <c r="P16" t="n">
-        <v>65.2</v>
+        <v>599.1197446017254</v>
       </c>
       <c r="Q16" t="n">
-        <v>65.2</v>
+        <v>545.6061898799506</v>
       </c>
       <c r="R16" t="n">
         <v>65.2</v>
@@ -5472,7 +5472,7 @@
         <v>284.0199739669084</v>
       </c>
       <c r="Y16" t="n">
-        <v>247.1862842199767</v>
+        <v>284.0199739669084</v>
       </c>
     </row>
     <row r="17">
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>880.1835184729979</v>
+        <v>883.6685602764463</v>
       </c>
       <c r="C17" t="n">
-        <v>707.9869747932061</v>
+        <v>711.4720165966545</v>
       </c>
       <c r="D17" t="n">
-        <v>575.3211609145699</v>
+        <v>578.8062027180183</v>
       </c>
       <c r="E17" t="n">
-        <v>448.6915754530864</v>
+        <v>452.1766172565348</v>
       </c>
       <c r="F17" t="n">
-        <v>321.5303343338825</v>
+        <v>325.0153761373309</v>
       </c>
       <c r="G17" t="n">
-        <v>195.5127865692196</v>
+        <v>198.9978283726681</v>
       </c>
       <c r="H17" t="n">
-        <v>65.2</v>
+        <v>68.68504180344846</v>
       </c>
       <c r="I17" t="n">
         <v>65.2</v>
@@ -5512,46 +5512,46 @@
         <v>1166.215479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>1166.215479385524</v>
+        <v>1973.065479385524</v>
       </c>
       <c r="M17" t="n">
-        <v>1677.064308114459</v>
+        <v>2483.914308114459</v>
       </c>
       <c r="N17" t="n">
-        <v>2290.284627889223</v>
+        <v>3097.134627889222</v>
       </c>
       <c r="O17" t="n">
-        <v>2821.400904947332</v>
+        <v>3260</v>
       </c>
       <c r="P17" t="n">
-        <v>2821.400904947332</v>
+        <v>3260</v>
       </c>
       <c r="Q17" t="n">
         <v>3260</v>
       </c>
       <c r="R17" t="n">
-        <v>3256.514958196551</v>
+        <v>3260</v>
       </c>
       <c r="S17" t="n">
-        <v>3038.486505870972</v>
+        <v>3041.971547674421</v>
       </c>
       <c r="T17" t="n">
-        <v>2727.703089983534</v>
+        <v>2731.188131786983</v>
       </c>
       <c r="U17" t="n">
-        <v>2353.742184378877</v>
+        <v>2357.227226182325</v>
       </c>
       <c r="V17" t="n">
-        <v>1999.347210472994</v>
+        <v>2002.832252276443</v>
       </c>
       <c r="W17" t="n">
-        <v>1636.343699381128</v>
+        <v>1639.828741184576</v>
       </c>
       <c r="X17" t="n">
-        <v>1319.897402956211</v>
+        <v>1323.382444759659</v>
       </c>
       <c r="Y17" t="n">
-        <v>1085.233329539235</v>
+        <v>1088.718371342683</v>
       </c>
     </row>
     <row r="18">
@@ -5585,25 +5585,25 @@
         <v>126.454877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>509.3868100677211</v>
+        <v>526.6213981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>698.5796261621044</v>
+        <v>869.9280986016793</v>
       </c>
       <c r="L18" t="n">
-        <v>969.9300877573046</v>
+        <v>1141.278560196879</v>
       </c>
       <c r="M18" t="n">
-        <v>1332.220629500164</v>
+        <v>1227.359101939739</v>
       </c>
       <c r="N18" t="n">
-        <v>1465.500914107732</v>
+        <v>1360.639386547307</v>
       </c>
       <c r="O18" t="n">
-        <v>1704.543365791451</v>
+        <v>1599.681838231026</v>
       </c>
       <c r="P18" t="n">
-        <v>1817.072710260958</v>
+        <v>1712.211182700533</v>
       </c>
       <c r="Q18" t="n">
         <v>1817.072710260958</v>
@@ -5640,55 +5640,55 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>422.6199739669084</v>
+        <v>414.0691125028051</v>
       </c>
       <c r="C19" t="n">
-        <v>428.8319797853442</v>
+        <v>420.2811183212409</v>
       </c>
       <c r="D19" t="n">
-        <v>428.8319797853442</v>
+        <v>420.2811183212409</v>
       </c>
       <c r="E19" t="n">
-        <v>428.8319797853442</v>
+        <v>420.2811183212409</v>
       </c>
       <c r="F19" t="n">
-        <v>433.4029523772797</v>
+        <v>424.8520909131764</v>
       </c>
       <c r="G19" t="n">
-        <v>467.019518264165</v>
+        <v>458.4686568000616</v>
       </c>
       <c r="H19" t="n">
-        <v>516.7461034235625</v>
+        <v>508.1952419594592</v>
       </c>
       <c r="I19" t="n">
-        <v>618.0889823596455</v>
+        <v>609.5381208955421</v>
       </c>
       <c r="J19" t="n">
-        <v>859.3827230120968</v>
+        <v>850.8318615479934</v>
       </c>
       <c r="K19" t="n">
-        <v>859.3827230120968</v>
+        <v>850.8318615479934</v>
       </c>
       <c r="L19" t="n">
-        <v>859.3827230120968</v>
+        <v>850.8318615479934</v>
       </c>
       <c r="M19" t="n">
-        <v>859.3827230120968</v>
+        <v>850.8318615479934</v>
       </c>
       <c r="N19" t="n">
-        <v>859.3827230120968</v>
+        <v>850.8318615479934</v>
       </c>
       <c r="O19" t="n">
-        <v>859.3827230120968</v>
+        <v>850.8318615479934</v>
       </c>
       <c r="P19" t="n">
-        <v>859.3827230120968</v>
+        <v>850.8318615479934</v>
       </c>
       <c r="Q19" t="n">
-        <v>517.3233615971224</v>
+        <v>601.5389976606127</v>
       </c>
       <c r="R19" t="n">
-        <v>65.2</v>
+        <v>149.4156360634904</v>
       </c>
       <c r="S19" t="n">
         <v>65.2</v>
@@ -5709,7 +5709,7 @@
         <v>422.6199739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>422.6199739669084</v>
+        <v>414.0691125028051</v>
       </c>
     </row>
     <row r="20">
@@ -5743,19 +5743,19 @@
         <v>65.2</v>
       </c>
       <c r="J20" t="n">
-        <v>65.2</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>774.9063663478685</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>1581.756366347868</v>
+        <v>890.4817564436345</v>
       </c>
       <c r="M20" t="n">
-        <v>2092.605195076803</v>
+        <v>1401.330585172569</v>
       </c>
       <c r="N20" t="n">
-        <v>2705.825514851566</v>
+        <v>2014.550904947333</v>
       </c>
       <c r="O20" t="n">
         <v>2821.400904947332</v>
@@ -5825,22 +5825,22 @@
         <v>250.4113981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>715.8142142372474</v>
+        <v>439.6042142372473</v>
       </c>
       <c r="L21" t="n">
-        <v>987.1646758324475</v>
+        <v>710.9546758324475</v>
       </c>
       <c r="M21" t="n">
-        <v>1073.245217575307</v>
+        <v>797.0352175753068</v>
       </c>
       <c r="N21" t="n">
-        <v>1206.525502182875</v>
+        <v>930.3155021828751</v>
       </c>
       <c r="O21" t="n">
-        <v>1704.543365791451</v>
+        <v>1323.471838231026</v>
       </c>
       <c r="P21" t="n">
-        <v>1817.072710260958</v>
+        <v>1712.211182700533</v>
       </c>
       <c r="Q21" t="n">
         <v>1817.072710260958</v>
@@ -5877,52 +5877,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>405.873354586564</v>
+        <v>422.6199739669084</v>
       </c>
       <c r="C22" t="n">
-        <v>412.0853604049998</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="D22" t="n">
-        <v>405.4831199448427</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="E22" t="n">
-        <v>405.4831199448427</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="F22" t="n">
-        <v>410.0540925367782</v>
+        <v>433.4029523772797</v>
       </c>
       <c r="G22" t="n">
-        <v>443.6706584236635</v>
+        <v>467.019518264165</v>
       </c>
       <c r="H22" t="n">
-        <v>493.3972435830611</v>
+        <v>516.7461034235625</v>
       </c>
       <c r="I22" t="n">
-        <v>594.7401225191441</v>
+        <v>618.0889823596455</v>
       </c>
       <c r="J22" t="n">
-        <v>836.0338631715954</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="K22" t="n">
-        <v>836.0338631715954</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="L22" t="n">
-        <v>690.0261579617174</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="M22" t="n">
-        <v>477.7736336649268</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="N22" t="n">
-        <v>477.7736336649268</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="O22" t="n">
-        <v>477.7736336649268</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="P22" t="n">
-        <v>65.2</v>
+        <v>446.80908934717</v>
       </c>
       <c r="Q22" t="n">
-        <v>65.2</v>
+        <v>446.80908934717</v>
       </c>
       <c r="R22" t="n">
         <v>65.2</v>
@@ -5946,7 +5946,7 @@
         <v>422.6199739669084</v>
       </c>
       <c r="Y22" t="n">
-        <v>414.0691125028051</v>
+        <v>422.6199739669084</v>
       </c>
     </row>
     <row r="23">
@@ -5956,16 +5956,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>880.1835184729979</v>
+        <v>883.6685602764463</v>
       </c>
       <c r="C23" t="n">
-        <v>707.9869747932061</v>
+        <v>711.4720165966545</v>
       </c>
       <c r="D23" t="n">
-        <v>575.3211609145699</v>
+        <v>578.8062027180183</v>
       </c>
       <c r="E23" t="n">
-        <v>448.6915754530864</v>
+        <v>452.1766172565348</v>
       </c>
       <c r="F23" t="n">
         <v>321.5303343338825</v>
@@ -5980,22 +5980,22 @@
         <v>65.2</v>
       </c>
       <c r="J23" t="n">
-        <v>65.2</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>774.9063663478685</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>1581.756366347868</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="M23" t="n">
-        <v>2092.605195076803</v>
+        <v>967.3579417665908</v>
       </c>
       <c r="N23" t="n">
-        <v>2705.825514851566</v>
+        <v>1580.578261541354</v>
       </c>
       <c r="O23" t="n">
-        <v>2705.825514851566</v>
+        <v>2387.428261541354</v>
       </c>
       <c r="P23" t="n">
         <v>2821.400904947332</v>
@@ -6007,25 +6007,25 @@
         <v>3260</v>
       </c>
       <c r="S23" t="n">
-        <v>3038.486505870972</v>
+        <v>3041.971547674421</v>
       </c>
       <c r="T23" t="n">
-        <v>2727.703089983534</v>
+        <v>2731.188131786983</v>
       </c>
       <c r="U23" t="n">
-        <v>2353.742184378877</v>
+        <v>2357.227226182325</v>
       </c>
       <c r="V23" t="n">
-        <v>1999.347210472994</v>
+        <v>2002.832252276443</v>
       </c>
       <c r="W23" t="n">
-        <v>1636.343699381128</v>
+        <v>1639.828741184576</v>
       </c>
       <c r="X23" t="n">
-        <v>1319.897402956211</v>
+        <v>1323.382444759659</v>
       </c>
       <c r="Y23" t="n">
-        <v>1085.233329539235</v>
+        <v>1088.718371342683</v>
       </c>
     </row>
     <row r="24">
@@ -6059,22 +6059,22 @@
         <v>126.454877967565</v>
       </c>
       <c r="J24" t="n">
-        <v>526.6213981428639</v>
+        <v>250.4113981428639</v>
       </c>
       <c r="K24" t="n">
-        <v>869.9280986016793</v>
+        <v>439.6042142372473</v>
       </c>
       <c r="L24" t="n">
-        <v>1141.278560196879</v>
+        <v>710.9546758324475</v>
       </c>
       <c r="M24" t="n">
-        <v>1227.359101939739</v>
+        <v>951.1491019397386</v>
       </c>
       <c r="N24" t="n">
-        <v>1360.639386547307</v>
+        <v>1084.429386547307</v>
       </c>
       <c r="O24" t="n">
-        <v>1599.681838231026</v>
+        <v>1323.471838231026</v>
       </c>
       <c r="P24" t="n">
         <v>1712.211182700533</v>
@@ -6123,43 +6123,43 @@
         <v>428.8319797853442</v>
       </c>
       <c r="E25" t="n">
-        <v>428.8319797853442</v>
+        <v>426.8310658086205</v>
       </c>
       <c r="F25" t="n">
-        <v>433.4029523772797</v>
+        <v>431.402038400556</v>
       </c>
       <c r="G25" t="n">
-        <v>467.019518264165</v>
+        <v>465.0186042874412</v>
       </c>
       <c r="H25" t="n">
-        <v>516.7461034235625</v>
+        <v>514.7451894468388</v>
       </c>
       <c r="I25" t="n">
-        <v>618.0889823596455</v>
+        <v>616.0880683829217</v>
       </c>
       <c r="J25" t="n">
-        <v>859.3827230120968</v>
+        <v>857.3818090353731</v>
       </c>
       <c r="K25" t="n">
-        <v>859.3827230120968</v>
+        <v>857.3818090353731</v>
       </c>
       <c r="L25" t="n">
-        <v>859.3827230120968</v>
+        <v>857.3818090353731</v>
       </c>
       <c r="M25" t="n">
-        <v>859.3827230120968</v>
+        <v>857.3818090353731</v>
       </c>
       <c r="N25" t="n">
-        <v>859.3827230120968</v>
+        <v>857.3818090353731</v>
       </c>
       <c r="O25" t="n">
-        <v>859.3827230120968</v>
+        <v>857.3818090353731</v>
       </c>
       <c r="P25" t="n">
-        <v>859.3827230120968</v>
+        <v>444.8081753704463</v>
       </c>
       <c r="Q25" t="n">
-        <v>408.0299286428058</v>
+        <v>65.2</v>
       </c>
       <c r="R25" t="n">
         <v>65.2</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1202.896245745725</v>
+        <v>193.1649250963515</v>
       </c>
       <c r="C26" t="n">
-        <v>976.1542475204787</v>
+        <v>60.64</v>
       </c>
       <c r="D26" t="n">
-        <v>788.9429790963881</v>
+        <v>60.64</v>
       </c>
       <c r="E26" t="n">
-        <v>607.76793908945</v>
+        <v>60.64</v>
       </c>
       <c r="F26" t="n">
-        <v>426.0612434247915</v>
+        <v>60.64</v>
       </c>
       <c r="G26" t="n">
-        <v>245.4982411146742</v>
+        <v>60.64</v>
       </c>
       <c r="H26" t="n">
         <v>60.64</v>
@@ -6223,19 +6223,19 @@
         <v>1161.655479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>1907.930851496302</v>
+        <v>1161.655479385524</v>
       </c>
       <c r="M26" t="n">
-        <v>2418.779680225237</v>
+        <v>1672.504308114459</v>
       </c>
       <c r="N26" t="n">
-        <v>3032</v>
+        <v>2285.724627889222</v>
       </c>
       <c r="O26" t="n">
-        <v>3032</v>
+        <v>2285.724627889222</v>
       </c>
       <c r="P26" t="n">
-        <v>3032</v>
+        <v>2593.400904947332</v>
       </c>
       <c r="Q26" t="n">
         <v>3032</v>
@@ -6253,16 +6253,16 @@
         <v>1939.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>1751.701039319847</v>
+        <v>1530.510435278166</v>
       </c>
       <c r="W26" t="n">
-        <v>1751.701039319847</v>
+        <v>1112.961469640845</v>
       </c>
       <c r="X26" t="n">
-        <v>1751.701039319847</v>
+        <v>741.9697186704736</v>
       </c>
       <c r="Y26" t="n">
-        <v>1462.491511357417</v>
+        <v>452.760190708043</v>
       </c>
     </row>
     <row r="27">
@@ -6293,25 +6293,25 @@
         <v>60.64</v>
       </c>
       <c r="I27" t="n">
-        <v>60.64</v>
+        <v>68.43487796756496</v>
       </c>
       <c r="J27" t="n">
-        <v>407.346520175299</v>
+        <v>415.1413981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>623.2599167834983</v>
+        <v>827.0842142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1117.360378378698</v>
+        <v>1321.184675832448</v>
       </c>
       <c r="M27" t="n">
-        <v>1426.190920121558</v>
+        <v>1630.015217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>1782.221204729126</v>
+        <v>1986.045502182875</v>
       </c>
       <c r="O27" t="n">
-        <v>2244.013656412845</v>
+        <v>2447.837953866594</v>
       </c>
       <c r="P27" t="n">
         <v>2579.293000882351</v>
@@ -6384,19 +6384,19 @@
         <v>404.8589893823512</v>
       </c>
       <c r="M28" t="n">
-        <v>106.2412000868462</v>
+        <v>404.8589893823512</v>
       </c>
       <c r="N28" t="n">
-        <v>60.64</v>
+        <v>404.8589893823512</v>
       </c>
       <c r="O28" t="n">
-        <v>60.64</v>
+        <v>404.8589893823512</v>
       </c>
       <c r="P28" t="n">
-        <v>60.64</v>
+        <v>404.8589893823512</v>
       </c>
       <c r="Q28" t="n">
-        <v>60.64</v>
+        <v>404.8589893823512</v>
       </c>
       <c r="R28" t="n">
         <v>60.64</v>
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>610.7330040956872</v>
+        <v>422.3780423170554</v>
       </c>
       <c r="C29" t="n">
-        <v>610.7330040956872</v>
+        <v>422.3780423170554</v>
       </c>
       <c r="D29" t="n">
-        <v>423.5217356715965</v>
+        <v>422.3780423170554</v>
       </c>
       <c r="E29" t="n">
-        <v>242.3466956646585</v>
+        <v>241.2030023101174</v>
       </c>
       <c r="F29" t="n">
-        <v>60.64</v>
+        <v>241.2030023101174</v>
       </c>
       <c r="G29" t="n">
         <v>60.64</v>
@@ -6454,25 +6454,25 @@
         <v>60.64</v>
       </c>
       <c r="J29" t="n">
-        <v>60.64</v>
+        <v>208.2333138773685</v>
       </c>
       <c r="K29" t="n">
-        <v>770.3463663478684</v>
+        <v>917.9396802252369</v>
       </c>
       <c r="L29" t="n">
-        <v>770.3463663478684</v>
+        <v>1668.359680225237</v>
       </c>
       <c r="M29" t="n">
-        <v>1281.195195076803</v>
+        <v>1668.359680225237</v>
       </c>
       <c r="N29" t="n">
-        <v>1894.415514851567</v>
+        <v>2281.58</v>
       </c>
       <c r="O29" t="n">
-        <v>2593.400904947332</v>
+        <v>2281.58</v>
       </c>
       <c r="P29" t="n">
-        <v>2593.400904947332</v>
+        <v>3032</v>
       </c>
       <c r="Q29" t="n">
         <v>3032</v>
@@ -6487,19 +6487,19 @@
         <v>2367.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>1939.450863729503</v>
+        <v>2168.663980950207</v>
       </c>
       <c r="V29" t="n">
-        <v>1530.510435278166</v>
+        <v>1759.72355249887</v>
       </c>
       <c r="W29" t="n">
-        <v>1112.961469640845</v>
+        <v>1342.174586861549</v>
       </c>
       <c r="X29" t="n">
-        <v>741.9697186704736</v>
+        <v>971.1828358911775</v>
       </c>
       <c r="Y29" t="n">
-        <v>610.7330040956872</v>
+        <v>681.9733079287469</v>
       </c>
     </row>
     <row r="30">
@@ -6530,28 +6530,28 @@
         <v>60.64</v>
       </c>
       <c r="I30" t="n">
-        <v>60.64</v>
+        <v>68.43487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>407.346520175299</v>
+        <v>415.1413981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>674.6614443439234</v>
+        <v>827.0842142372474</v>
       </c>
       <c r="L30" t="n">
-        <v>1168.761905939124</v>
+        <v>1321.184675832448</v>
       </c>
       <c r="M30" t="n">
-        <v>1477.592447681983</v>
+        <v>1426.190920121558</v>
       </c>
       <c r="N30" t="n">
-        <v>1833.622732289551</v>
+        <v>1782.221204729126</v>
       </c>
       <c r="O30" t="n">
-        <v>2295.41518397327</v>
+        <v>2244.013656412845</v>
       </c>
       <c r="P30" t="n">
-        <v>2630.694528442777</v>
+        <v>2579.293000882351</v>
       </c>
       <c r="Q30" t="n">
         <v>2630.694528442777</v>
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>230.350601658763</v>
+        <v>174.3382646830374</v>
       </c>
       <c r="C31" t="n">
-        <v>182.1432818122532</v>
+        <v>174.3382646830374</v>
       </c>
       <c r="D31" t="n">
-        <v>120.9955868066416</v>
+        <v>174.3382646830374</v>
       </c>
       <c r="E31" t="n">
-        <v>64.44921828446326</v>
+        <v>174.3382646830374</v>
       </c>
       <c r="F31" t="n">
-        <v>64.44921828446326</v>
+        <v>174.3382646830374</v>
       </c>
       <c r="G31" t="n">
-        <v>64.44921828446326</v>
+        <v>174.3382646830374</v>
       </c>
       <c r="H31" t="n">
+        <v>174.3382646830374</v>
+      </c>
+      <c r="I31" t="n">
+        <v>222.2211436191203</v>
+      </c>
+      <c r="J31" t="n">
+        <v>410.0548842715717</v>
+      </c>
+      <c r="K31" t="n">
+        <v>410.0548842715717</v>
+      </c>
+      <c r="L31" t="n">
+        <v>410.0548842715717</v>
+      </c>
+      <c r="M31" t="n">
+        <v>111.4370949760667</v>
+      </c>
+      <c r="N31" t="n">
         <v>60.64</v>
       </c>
-      <c r="I31" t="n">
-        <v>108.5228789360829</v>
-      </c>
-      <c r="J31" t="n">
-        <v>296.3566195885343</v>
-      </c>
-      <c r="K31" t="n">
-        <v>296.3566195885343</v>
-      </c>
-      <c r="L31" t="n">
-        <v>296.3566195885343</v>
-      </c>
-      <c r="M31" t="n">
-        <v>296.3566195885343</v>
-      </c>
-      <c r="N31" t="n">
-        <v>296.3566195885343</v>
-      </c>
       <c r="O31" t="n">
-        <v>296.3566195885343</v>
+        <v>60.64</v>
       </c>
       <c r="P31" t="n">
-        <v>296.3566195885343</v>
+        <v>60.64</v>
       </c>
       <c r="Q31" t="n">
-        <v>296.3566195885343</v>
+        <v>60.64</v>
       </c>
       <c r="R31" t="n">
-        <v>296.3566195885343</v>
+        <v>60.64</v>
       </c>
       <c r="S31" t="n">
-        <v>266.5468909710369</v>
+        <v>60.64</v>
       </c>
       <c r="T31" t="n">
-        <v>281.3725701298418</v>
+        <v>75.46567915880486</v>
       </c>
       <c r="U31" t="n">
-        <v>354.6737627681284</v>
+        <v>148.7668717970915</v>
       </c>
       <c r="V31" t="n">
-        <v>380.2451556540744</v>
+        <v>174.3382646830374</v>
       </c>
       <c r="W31" t="n">
-        <v>378.8584790493171</v>
+        <v>174.3382646830374</v>
       </c>
       <c r="X31" t="n">
-        <v>356.1881301300165</v>
+        <v>174.3382646830374</v>
       </c>
       <c r="Y31" t="n">
-        <v>293.0918141204586</v>
+        <v>174.3382646830374</v>
       </c>
     </row>
     <row r="32">
@@ -6676,13 +6676,13 @@
         <v>401.3112532230692</v>
       </c>
       <c r="E32" t="n">
-        <v>401.3112532230692</v>
+        <v>279.7321728120908</v>
       </c>
       <c r="F32" t="n">
-        <v>279.2005171543703</v>
+        <v>279.7321728120908</v>
       </c>
       <c r="G32" t="n">
-        <v>158.2334744402125</v>
+        <v>158.765130097933</v>
       </c>
       <c r="H32" t="n">
         <v>60.64</v>
@@ -6691,22 +6691,22 @@
         <v>60.64</v>
       </c>
       <c r="J32" t="n">
-        <v>60.64</v>
+        <v>444.6577074152185</v>
       </c>
       <c r="K32" t="n">
-        <v>770.3463663478684</v>
+        <v>444.6577074152185</v>
       </c>
       <c r="L32" t="n">
-        <v>770.3463663478684</v>
+        <v>444.6577074152185</v>
       </c>
       <c r="M32" t="n">
-        <v>1276.330929891318</v>
+        <v>950.6422709586681</v>
       </c>
       <c r="N32" t="n">
-        <v>1200.073681905018</v>
+        <v>1561.076881482863</v>
       </c>
       <c r="O32" t="n">
-        <v>1849.312132381729</v>
+        <v>2169.601698307362</v>
       </c>
       <c r="P32" t="n">
         <v>2599.732132381729</v>
@@ -6770,16 +6770,16 @@
         <v>126.844877967565</v>
       </c>
       <c r="J33" t="n">
-        <v>314.3077067497201</v>
+        <v>531.9613981428638</v>
       </c>
       <c r="K33" t="n">
-        <v>503.5005228441035</v>
+        <v>721.1542142372472</v>
       </c>
       <c r="L33" t="n">
-        <v>774.8509844393036</v>
+        <v>992.5046758324472</v>
       </c>
       <c r="M33" t="n">
-        <v>860.9315261821629</v>
+        <v>1078.585217575306</v>
       </c>
       <c r="N33" t="n">
         <v>1275.371810789731</v>
@@ -6861,13 +6861,13 @@
         <v>912.2616272235098</v>
       </c>
       <c r="N34" t="n">
-        <v>622.1756926056462</v>
+        <v>912.2616272235098</v>
       </c>
       <c r="O34" t="n">
-        <v>262.1296682834088</v>
+        <v>912.2616272235098</v>
       </c>
       <c r="P34" t="n">
-        <v>60.64</v>
+        <v>504.7384986090881</v>
       </c>
       <c r="Q34" t="n">
         <v>60.64</v>
@@ -6931,22 +6931,22 @@
         <v>444.6577074152185</v>
       </c>
       <c r="K35" t="n">
-        <v>1154.364073763087</v>
+        <v>429.4211417586528</v>
       </c>
       <c r="L35" t="n">
-        <v>1143.272607030799</v>
+        <v>414.184576102087</v>
       </c>
       <c r="M35" t="n">
-        <v>1128.036041374233</v>
+        <v>920.1691396455365</v>
       </c>
       <c r="N35" t="n">
-        <v>1531.160000000012</v>
+        <v>1530.603750169731</v>
       </c>
       <c r="O35" t="n">
-        <v>2281.580000000012</v>
+        <v>1849.312132381729</v>
       </c>
       <c r="P35" t="n">
-        <v>3032.000000000012</v>
+        <v>2599.732132381729</v>
       </c>
       <c r="Q35" t="n">
         <v>3032</v>
@@ -6961,13 +6961,13 @@
         <v>2517.329545928397</v>
       </c>
       <c r="U35" t="n">
-        <v>2271.404406601099</v>
+        <v>2150.439347394447</v>
       </c>
       <c r="V35" t="n">
-        <v>1924.080139765923</v>
+        <v>1803.115080559271</v>
       </c>
       <c r="W35" t="n">
-        <v>1568.147335744764</v>
+        <v>1447.182276538112</v>
       </c>
       <c r="X35" t="n">
         <v>1258.771746390554</v>
@@ -7007,22 +7007,22 @@
         <v>128.824877967565</v>
       </c>
       <c r="J36" t="n">
-        <v>252.7813981428639</v>
+        <v>280.0446764466896</v>
       </c>
       <c r="K36" t="n">
-        <v>441.9742142372473</v>
+        <v>469.2374925410729</v>
       </c>
       <c r="L36" t="n">
-        <v>713.3246758324474</v>
+        <v>1023.727954136273</v>
       </c>
       <c r="M36" t="n">
-        <v>799.4052175753067</v>
+        <v>1109.808495879132</v>
       </c>
       <c r="N36" t="n">
-        <v>932.685502182875</v>
+        <v>1243.088780486701</v>
       </c>
       <c r="O36" t="n">
-        <v>1454.867953866594</v>
+        <v>1482.13123217042</v>
       </c>
       <c r="P36" t="n">
         <v>1594.660576639926</v>
@@ -7062,52 +7062,52 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>451.2298195735121</v>
+        <v>452.7099739669085</v>
       </c>
       <c r="C37" t="n">
-        <v>464.3718253919479</v>
+        <v>465.8519797853443</v>
       </c>
       <c r="D37" t="n">
-        <v>464.830969516948</v>
+        <v>466.3111239103443</v>
       </c>
       <c r="E37" t="n">
-        <v>469.799873728361</v>
+        <v>471.2800281217574</v>
       </c>
       <c r="F37" t="n">
-        <v>481.3008463202965</v>
+        <v>482.7810007136928</v>
       </c>
       <c r="G37" t="n">
-        <v>521.8474122071817</v>
+        <v>523.3275666005781</v>
       </c>
       <c r="H37" t="n">
-        <v>578.5039973665793</v>
+        <v>579.9841517599756</v>
       </c>
       <c r="I37" t="n">
-        <v>686.7768763026622</v>
+        <v>688.2570306960586</v>
       </c>
       <c r="J37" t="n">
-        <v>935.0006169551135</v>
+        <v>936.4807713485098</v>
       </c>
       <c r="K37" t="n">
-        <v>932.4543807923428</v>
+        <v>936.4807713485098</v>
       </c>
       <c r="L37" t="n">
-        <v>793.5173826531719</v>
+        <v>936.4807713485098</v>
       </c>
       <c r="M37" t="n">
-        <v>556.5157549738286</v>
+        <v>936.4807713485098</v>
       </c>
       <c r="N37" t="n">
-        <v>556.5157549738286</v>
+        <v>936.4807713485098</v>
       </c>
       <c r="O37" t="n">
-        <v>556.5157549738286</v>
+        <v>936.4807713485098</v>
       </c>
       <c r="P37" t="n">
-        <v>556.5157549738286</v>
+        <v>530.9778447542901</v>
       </c>
       <c r="Q37" t="n">
-        <v>112.2336676752448</v>
+        <v>505.6926545264152</v>
       </c>
       <c r="R37" t="n">
         <v>60.64</v>
@@ -7131,7 +7131,7 @@
         <v>452.7099739669085</v>
       </c>
       <c r="Y37" t="n">
-        <v>451.2298195735121</v>
+        <v>452.7099739669085</v>
       </c>
     </row>
     <row r="38">
@@ -7144,19 +7144,19 @@
         <v>712.2342168421035</v>
       </c>
       <c r="C38" t="n">
-        <v>668.0734394396707</v>
+        <v>547.1083802330187</v>
       </c>
       <c r="D38" t="n">
-        <v>542.4783326317415</v>
+        <v>421.5132734250896</v>
       </c>
       <c r="E38" t="n">
-        <v>422.9194542409651</v>
+        <v>421.5132734250896</v>
       </c>
       <c r="F38" t="n">
-        <v>302.8289201924683</v>
+        <v>301.4227393765927</v>
       </c>
       <c r="G38" t="n">
-        <v>183.8820794985126</v>
+        <v>182.475898682637</v>
       </c>
       <c r="H38" t="n">
         <v>60.64</v>
@@ -7168,19 +7168,19 @@
         <v>444.6577074152185</v>
       </c>
       <c r="K38" t="n">
-        <v>758.3943390248679</v>
+        <v>1154.364073763087</v>
       </c>
       <c r="L38" t="n">
-        <v>748.1295239706506</v>
+        <v>1143.272607030799</v>
       </c>
       <c r="M38" t="n">
-        <v>1254.1140875141</v>
+        <v>1649.257170574249</v>
       </c>
       <c r="N38" t="n">
-        <v>1864.548698038295</v>
+        <v>1634.020604917683</v>
       </c>
       <c r="O38" t="n">
-        <v>2614.968698038295</v>
+        <v>1849.312132381729</v>
       </c>
       <c r="P38" t="n">
         <v>2599.732132381729</v>
@@ -7244,13 +7244,13 @@
         <v>128.824877967565</v>
       </c>
       <c r="J39" t="n">
-        <v>280.0446764466896</v>
+        <v>252.7813981428639</v>
       </c>
       <c r="K39" t="n">
-        <v>469.2374925410729</v>
+        <v>469.237492541073</v>
       </c>
       <c r="L39" t="n">
-        <v>1023.727954136273</v>
+        <v>740.5879541362731</v>
       </c>
       <c r="M39" t="n">
         <v>1109.808495879132</v>
@@ -7344,10 +7344,10 @@
         <v>936.4807713485098</v>
       </c>
       <c r="Q40" t="n">
-        <v>582.8375835191985</v>
+        <v>492.198684049926</v>
       </c>
       <c r="R40" t="n">
-        <v>137.7849289927833</v>
+        <v>60.64</v>
       </c>
       <c r="S40" t="n">
         <v>60.64</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>444.6793826272344</v>
+        <v>476.6134686695391</v>
       </c>
       <c r="C41" t="n">
-        <v>216.927283391887</v>
+        <v>248.8613694341917</v>
       </c>
       <c r="D41" t="n">
-        <v>216.927283391887</v>
+        <v>60.64</v>
       </c>
       <c r="E41" t="n">
-        <v>216.927283391887</v>
+        <v>60.64</v>
       </c>
       <c r="F41" t="n">
-        <v>216.927283391887</v>
+        <v>60.64</v>
       </c>
       <c r="G41" t="n">
-        <v>216.927283391887</v>
+        <v>60.64</v>
       </c>
       <c r="H41" t="n">
         <v>60.64</v>
@@ -7402,52 +7402,52 @@
         <v>60.64</v>
       </c>
       <c r="J41" t="n">
-        <v>60.64</v>
+        <v>451.9491130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>407.0908514962982</v>
+        <v>1161.655479385524</v>
       </c>
       <c r="L41" t="n">
-        <v>1157.510851496298</v>
+        <v>1161.655479385524</v>
       </c>
       <c r="M41" t="n">
-        <v>1668.359680225233</v>
+        <v>1672.504308114459</v>
       </c>
       <c r="N41" t="n">
-        <v>2281.579999999996</v>
+        <v>2285.724627889222</v>
       </c>
       <c r="O41" t="n">
-        <v>3032</v>
+        <v>2593.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>3032</v>
+        <v>2593.400904947332</v>
       </c>
       <c r="Q41" t="n">
         <v>3032</v>
       </c>
       <c r="R41" t="n">
-        <v>3004.84990017344</v>
+        <v>3007.169723865005</v>
       </c>
       <c r="S41" t="n">
-        <v>2731.265892292306</v>
+        <v>2733.585715983871</v>
       </c>
       <c r="T41" t="n">
-        <v>2364.926920849312</v>
+        <v>2367.246744540877</v>
       </c>
       <c r="U41" t="n">
-        <v>1935.410459689099</v>
+        <v>1937.730283380664</v>
       </c>
       <c r="V41" t="n">
-        <v>1525.45993022766</v>
+        <v>1527.779753919226</v>
       </c>
       <c r="W41" t="n">
-        <v>1106.900863580239</v>
+        <v>1109.220687271804</v>
       </c>
       <c r="X41" t="n">
-        <v>734.8990115997661</v>
+        <v>737.2188352913315</v>
       </c>
       <c r="Y41" t="n">
-        <v>444.6793826272344</v>
+        <v>737.2188352913315</v>
       </c>
     </row>
     <row r="42">
@@ -7478,10 +7478,10 @@
         <v>60.64</v>
       </c>
       <c r="I42" t="n">
-        <v>60.64</v>
+        <v>67.44487796756495</v>
       </c>
       <c r="J42" t="n">
-        <v>233.3986158406288</v>
+        <v>413.1613981428639</v>
       </c>
       <c r="K42" t="n">
         <v>644.3514319350122</v>
@@ -7536,49 +7536,49 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>137.9049146506891</v>
+        <v>137.9049146507114</v>
       </c>
       <c r="C43" t="n">
-        <v>137.9049146506891</v>
+        <v>137.9049146507114</v>
       </c>
       <c r="D43" t="n">
-        <v>137.9049146506891</v>
+        <v>137.9049146507114</v>
       </c>
       <c r="E43" t="n">
-        <v>137.9049146506891</v>
+        <v>137.9049146507114</v>
       </c>
       <c r="F43" t="n">
-        <v>87.01314094589921</v>
+        <v>137.9049146507114</v>
       </c>
       <c r="G43" t="n">
-        <v>65.75670373223251</v>
+        <v>137.9049146507114</v>
       </c>
       <c r="H43" t="n">
-        <v>60.93738443766824</v>
+        <v>133.0855953561471</v>
       </c>
       <c r="I43" t="n">
-        <v>107.8302633737512</v>
+        <v>179.9784742922301</v>
       </c>
       <c r="J43" t="n">
-        <v>294.6740040262025</v>
+        <v>366.8222149446814</v>
       </c>
       <c r="K43" t="n">
-        <v>229.5015052371691</v>
+        <v>366.8222149446814</v>
       </c>
       <c r="L43" t="n">
-        <v>60.64</v>
+        <v>366.8222149446814</v>
       </c>
       <c r="M43" t="n">
-        <v>60.64</v>
+        <v>366.8222149446814</v>
       </c>
       <c r="N43" t="n">
-        <v>60.64</v>
+        <v>366.8222149446814</v>
       </c>
       <c r="O43" t="n">
-        <v>60.64</v>
+        <v>366.8222149446814</v>
       </c>
       <c r="P43" t="n">
-        <v>60.64</v>
+        <v>366.8222149446814</v>
       </c>
       <c r="Q43" t="n">
         <v>60.64</v>
@@ -7593,19 +7593,19 @@
         <v>74.47567915880487</v>
       </c>
       <c r="U43" t="n">
-        <v>140.3016922655473</v>
+        <v>140.3016922655697</v>
       </c>
       <c r="V43" t="n">
-        <v>140.3016922655473</v>
+        <v>140.3016922655697</v>
       </c>
       <c r="W43" t="n">
-        <v>137.9049146506891</v>
+        <v>137.9049146507114</v>
       </c>
       <c r="X43" t="n">
-        <v>137.9049146506891</v>
+        <v>137.9049146507114</v>
       </c>
       <c r="Y43" t="n">
-        <v>137.9049146506891</v>
+        <v>137.9049146507114</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>904.6821543012704</v>
+        <v>529.1387211947916</v>
       </c>
       <c r="C44" t="n">
-        <v>904.6821543012704</v>
+        <v>275.123995696818</v>
       </c>
       <c r="D44" t="n">
-        <v>690.1981586044525</v>
+        <v>60.64</v>
       </c>
       <c r="E44" t="n">
-        <v>481.7503913247871</v>
+        <v>60.64</v>
       </c>
       <c r="F44" t="n">
-        <v>272.7709683874014</v>
+        <v>60.64</v>
       </c>
       <c r="G44" t="n">
-        <v>272.7709683874014</v>
+        <v>60.64</v>
       </c>
       <c r="H44" t="n">
         <v>60.64</v>
@@ -7666,25 +7666,25 @@
         <v>2978.587273910814</v>
       </c>
       <c r="S44" t="n">
-        <v>2978.587273910814</v>
+        <v>2678.740639767053</v>
       </c>
       <c r="T44" t="n">
-        <v>2787.331729298058</v>
+        <v>2678.740639767053</v>
       </c>
       <c r="U44" t="n">
-        <v>2787.331729298058</v>
+        <v>2222.961552344214</v>
       </c>
       <c r="V44" t="n">
-        <v>2351.118573573994</v>
+        <v>1975.575140467515</v>
       </c>
       <c r="W44" t="n">
-        <v>1906.296880663946</v>
+        <v>1530.753447557467</v>
       </c>
       <c r="X44" t="n">
-        <v>1508.032402420847</v>
+        <v>1132.488969314368</v>
       </c>
       <c r="Y44" t="n">
-        <v>1191.550147185689</v>
+        <v>816.0067140792103</v>
       </c>
     </row>
     <row r="45">
@@ -7694,19 +7694,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>949.9126746018267</v>
+        <v>669.430631397049</v>
       </c>
       <c r="C45" t="n">
-        <v>785.1652882932214</v>
+        <v>504.6832450884436</v>
       </c>
       <c r="D45" t="n">
-        <v>633.713079305643</v>
+        <v>504.6832450884436</v>
       </c>
       <c r="E45" t="n">
-        <v>487.5796477683575</v>
+        <v>358.5498135511581</v>
       </c>
       <c r="F45" t="n">
-        <v>344.5127363159566</v>
+        <v>215.4829020987573</v>
       </c>
       <c r="G45" t="n">
         <v>215.4829020987573</v>
@@ -7724,46 +7724,46 @@
         <v>765.8293362696824</v>
       </c>
       <c r="L45" t="n">
-        <v>1155.906962624539</v>
+        <v>1233.199797864882</v>
       </c>
       <c r="M45" t="n">
-        <v>1438.007504367398</v>
+        <v>1515.300339607742</v>
       </c>
       <c r="N45" t="n">
-        <v>1767.307788974967</v>
+        <v>1844.60062421531</v>
       </c>
       <c r="O45" t="n">
-        <v>2202.370240658685</v>
+        <v>2279.663075899029</v>
       </c>
       <c r="P45" t="n">
-        <v>2510.919585128192</v>
+        <v>2469.559486407321</v>
       </c>
       <c r="Q45" t="n">
-        <v>2535.591112688617</v>
+        <v>2494.231013967747</v>
       </c>
       <c r="R45" t="n">
-        <v>2435.026436154249</v>
+        <v>2141.429198520899</v>
       </c>
       <c r="S45" t="n">
-        <v>2435.026436154249</v>
+        <v>1870.152430879877</v>
       </c>
       <c r="T45" t="n">
-        <v>2225.57414805575</v>
+        <v>1660.700142781378</v>
       </c>
       <c r="U45" t="n">
-        <v>2021.321259409097</v>
+        <v>1660.700142781378</v>
       </c>
       <c r="V45" t="n">
-        <v>1802.623615781298</v>
+        <v>1442.00249915358</v>
       </c>
       <c r="W45" t="n">
-        <v>1565.883067387532</v>
+        <v>1205.261950759814</v>
       </c>
       <c r="X45" t="n">
-        <v>1341.779290169969</v>
+        <v>1061.297246965191</v>
       </c>
       <c r="Y45" t="n">
-        <v>1138.353640911248</v>
+        <v>857.8715977064699</v>
       </c>
     </row>
     <row r="46">
@@ -7773,22 +7773,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>60.64</v>
+        <v>91.72194555719052</v>
       </c>
       <c r="C46" t="n">
-        <v>60.64</v>
+        <v>91.72194555719052</v>
       </c>
       <c r="D46" t="n">
-        <v>60.64</v>
+        <v>91.72194555719052</v>
       </c>
       <c r="E46" t="n">
-        <v>60.64</v>
+        <v>91.72194555719052</v>
       </c>
       <c r="F46" t="n">
-        <v>60.64</v>
+        <v>91.72194555719052</v>
       </c>
       <c r="G46" t="n">
-        <v>60.64</v>
+        <v>91.72194555719052</v>
       </c>
       <c r="H46" t="n">
         <v>60.64</v>
@@ -7797,52 +7797,52 @@
         <v>60.64</v>
       </c>
       <c r="J46" t="n">
-        <v>60.64</v>
+        <v>133.7095077402043</v>
       </c>
       <c r="K46" t="n">
-        <v>60.64</v>
+        <v>133.7095077402043</v>
       </c>
       <c r="L46" t="n">
-        <v>60.64</v>
+        <v>133.7095077402043</v>
       </c>
       <c r="M46" t="n">
-        <v>60.64</v>
+        <v>133.7095077402043</v>
       </c>
       <c r="N46" t="n">
-        <v>60.64</v>
+        <v>133.7095077402043</v>
       </c>
       <c r="O46" t="n">
-        <v>60.64</v>
+        <v>133.7095077402043</v>
       </c>
       <c r="P46" t="n">
-        <v>60.64</v>
+        <v>133.7095077402043</v>
       </c>
       <c r="Q46" t="n">
-        <v>60.64</v>
+        <v>133.7095077402043</v>
       </c>
       <c r="R46" t="n">
-        <v>60.64</v>
+        <v>133.7095077402043</v>
       </c>
       <c r="S46" t="n">
-        <v>60.64</v>
+        <v>133.7095077402043</v>
       </c>
       <c r="T46" t="n">
-        <v>60.64</v>
+        <v>121.5634809662066</v>
       </c>
       <c r="U46" t="n">
-        <v>60.64</v>
+        <v>121.5634809662066</v>
       </c>
       <c r="V46" t="n">
-        <v>60.64</v>
+        <v>120.3813494346751</v>
       </c>
       <c r="W46" t="n">
-        <v>60.64</v>
+        <v>91.72194555719052</v>
       </c>
       <c r="X46" t="n">
-        <v>60.64</v>
+        <v>91.72194555719052</v>
       </c>
       <c r="Y46" t="n">
-        <v>60.64</v>
+        <v>91.72194555719052</v>
       </c>
     </row>
   </sheetData>
@@ -7967,13 +7967,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>40.66296549026548</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
-        <v>783.0093003026025</v>
+        <v>814.9999999999995</v>
       </c>
       <c r="M2" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N2" t="n">
         <v>477.2489580698352</v>
@@ -7982,10 +7982,10 @@
         <v>885.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>815.2870600406815</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q2" t="n">
-        <v>615.8520732695737</v>
+        <v>206.6403036313278</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8204,22 +8204,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>601.3737659428016</v>
+        <v>783.0093003027089</v>
       </c>
       <c r="M5" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>1096.663422488788</v>
+        <v>517.9119235599961</v>
       </c>
       <c r="O5" t="n">
-        <v>70.24786957409242</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2870600406814674</v>
+        <v>815.2870600406815</v>
       </c>
       <c r="Q5" t="n">
         <v>615.8520732695737</v>
@@ -8438,13 +8438,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>430.3047365861567</v>
+        <v>51.26150624509023</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>165.4169962838681</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
@@ -8453,10 +8453,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>885.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P8" t="n">
-        <v>503.5359435065877</v>
+        <v>815.2870600406815</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -8675,10 +8675,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>53.6609420467414</v>
       </c>
       <c r="K11" t="n">
-        <v>438.3562054605845</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>815</v>
@@ -8690,7 +8690,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>70.24786957409245</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>151.7858245236418</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,7 +8927,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>606.7289575115773</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
@@ -9155,7 +9155,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,13 +9164,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>606.7289575115773</v>
+        <v>234.7583464536658</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,13 +9386,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>814.9999999999999</v>
+        <v>438.3562054605846</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9401,7 +9401,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>186.9906878526441</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
@@ -9623,13 +9623,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>814.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,10 +9638,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>117.0298783192331</v>
+        <v>438.6432655012658</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9866,7 +9866,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>753.8135071826036</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9878,10 +9878,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>311.071178281197</v>
       </c>
       <c r="Q26" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,28 +10097,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>35.04300624509033</v>
+        <v>184.1271616767757</v>
       </c>
       <c r="K29" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>758</v>
       </c>
       <c r="M29" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N29" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>776.2937181556742</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2870600406814136</v>
+        <v>758.2870600406815</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,10 +10334,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>50.12720624509029</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10346,13 +10346,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>401.7542825633989</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>726.0442841970324</v>
+        <v>684.9194017200518</v>
       </c>
       <c r="P32" t="n">
-        <v>758.2870600406815</v>
+        <v>441.2003897743044</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10574,25 +10574,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423167</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>891.4258771093566</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>828.2478695740924</v>
+        <v>395.9313348676455</v>
       </c>
       <c r="P35" t="n">
         <v>758.2870600406815</v>
       </c>
       <c r="Q35" t="n">
-        <v>187.9068843274732</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,7 +10811,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>325.6834652935528</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10820,13 +10820,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O38" t="n">
-        <v>828.2478695740924</v>
+        <v>298.470681763498</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2870600406814674</v>
+        <v>758.2870600406815</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11045,13 +11045,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>349.9503550467658</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>758</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
@@ -11060,13 +11060,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>828.2478695740964</v>
+        <v>381.031987814608</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -23232,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>148.4388833579632</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
         <v>179.8896287080119</v>
@@ -23271,7 +23271,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -23280,7 +23280,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>424.2212965486107</v>
+        <v>419.1754891279998</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -23469,13 +23469,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>82.42914672070054</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>9.698784447761966</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23520,7 +23520,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>378.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -23648,13 +23648,13 @@
         <v>37.52077380114304</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N16" t="n">
-        <v>270.2491205257682</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O16" t="n">
         <v>389.445564079015</v>
@@ -23663,10 +23663,10 @@
         <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>474.839266425598</v>
+        <v>421.860847251041</v>
       </c>
       <c r="R16" t="n">
-        <v>475.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>111.3734797028554</v>
@@ -23687,7 +23687,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -23900,13 +23900,13 @@
         <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>108.2004986247733</v>
+        <v>200.0393311770911</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23924,7 +23924,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -24092,13 +24092,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E22" t="n">
         <v>1.98090483695654</v>
@@ -24122,10 +24122,10 @@
         <v>9.520773801143037</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M22" t="n">
-        <v>31.50161234872709</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N22" t="n">
         <v>292.1850752716849</v>
@@ -24140,7 +24140,7 @@
         <v>446.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>447.6021279811511</v>
+        <v>69.80912952745274</v>
       </c>
       <c r="S22" t="n">
         <v>83.37347970285543</v>
@@ -24161,7 +24161,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>8.465352849462363</v>
       </c>
     </row>
     <row r="23">
@@ -24338,7 +24338,7 @@
         <v>6.53621805555548</v>
       </c>
       <c r="E25" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -24371,13 +24371,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>71.02717280885616</v>
       </c>
       <c r="R25" t="n">
-        <v>108.2004986247733</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>93.2749023976059</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24468,13 +24468,13 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>218.9786980012645</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>413.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>367.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -24599,10 +24599,10 @@
         <v>198.5476281577792</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>301.0398871857072</v>
+        <v>346.1850752716849</v>
       </c>
       <c r="O28" t="n">
         <v>415.445564079015</v>
@@ -24614,7 +24614,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S28" t="n">
         <v>137.3734797028554</v>
@@ -24645,22 +24645,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>256.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>224.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>183.0096587035274</v>
@@ -24702,7 +24702,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>226.9209860484969</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -24714,7 +24714,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>156.3930852537678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -24803,16 +24803,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F31" t="n">
         <v>49.38285596774193</v>
@@ -24821,7 +24821,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24836,10 +24836,10 @@
         <v>198.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>346.1850752716849</v>
+        <v>295.8959512453789</v>
       </c>
       <c r="O31" t="n">
         <v>415.445564079015</v>
@@ -24854,7 +24854,7 @@
         <v>501.6021279811511</v>
       </c>
       <c r="S31" t="n">
-        <v>107.8618483715331</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24866,13 +24866,13 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="32">
@@ -24891,16 +24891,16 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>120.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>120.8896287080119</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>27.39211900771699</v>
+        <v>26.86577990657376</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -25076,16 +25076,16 @@
         <v>236.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>287.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>356.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>203.9731257277027</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>441.839266425598</v>
+        <v>2.181752802600784</v>
       </c>
       <c r="R34" t="n">
         <v>442.6021279811511</v>
@@ -25176,7 +25176,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>119.7554086145852</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -25185,7 +25185,7 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>119.7554086145854</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -25304,13 +25304,13 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>2.520773801143037</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>137.5476281577792</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>234.6316114025499</v>
       </c>
       <c r="N37" t="n">
         <v>285.1850752716849</v>
@@ -25319,13 +25319,13 @@
         <v>354.445564079015</v>
       </c>
       <c r="P37" t="n">
-        <v>401.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>414.8069281000018</v>
       </c>
       <c r="R37" t="n">
-        <v>389.5243969826587</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>76.37347970285543</v>
@@ -25346,7 +25346,7 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.465352849462363</v>
       </c>
     </row>
     <row r="38">
@@ -25359,13 +25359,13 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>119.7554086145854</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>118.3632896068686</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -25374,7 +25374,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1.392119007716815</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25559,13 +25559,13 @@
         <v>401.4478973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>89.73251047457973</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>13.35903077172429</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>76.37347970285543</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25593,13 +25593,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>257.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>186.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>180.3632896068686</v>
@@ -25611,7 +25611,7 @@
         <v>179.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>29.28524814555928</v>
+        <v>184.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,7 +25641,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.296625454649359</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -25662,7 +25662,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>287.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -25763,10 +25763,10 @@
         <v>56.98090483695654</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>50.38285596774193</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>21.04387284153003</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -25778,10 +25778,10 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>64.52077380114304</v>
       </c>
       <c r="L43" t="n">
-        <v>32.37473797298173</v>
+        <v>199.5476281577792</v>
       </c>
       <c r="M43" t="n">
         <v>296.6316114025499</v>
@@ -25796,7 +25796,7 @@
         <v>463.4478973282775</v>
       </c>
       <c r="Q43" t="n">
-        <v>501.839266425598</v>
+        <v>198.7188736303634</v>
       </c>
       <c r="R43" t="n">
         <v>502.6021279811511</v>
@@ -25833,22 +25833,22 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>251.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>206.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>206.8896287080119</v>
       </c>
       <c r="G44" t="n">
         <v>205.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>210.0096587035274</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25881,16 +25881,16 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>296.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>199.3325925619361</v>
+        <v>388.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>451.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>186.9384764088919</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -25915,7 +25915,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>149.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -25924,7 +25924,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>127.7395358750273</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -25957,16 +25957,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>249.7147675233544</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>268.5639999646113</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>202.2103597601867</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -25975,7 +25975,7 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>79.33768268871111</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -26006,7 +26006,7 @@
         <v>47.04387284153003</v>
       </c>
       <c r="H46" t="n">
-        <v>30.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -26042,16 +26042,16 @@
         <v>164.3734797028554</v>
       </c>
       <c r="T46" t="n">
-        <v>12.02456650625771</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.170310216216194</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>28.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>49.44364543010755</v>
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2294104.66156081</v>
+        <v>2294104.661560809</v>
       </c>
     </row>
     <row r="5">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4226692.448034385</v>
+        <v>4226692.448034386</v>
       </c>
     </row>
     <row r="8">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6779769.381181151</v>
+        <v>6779769.381181149</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7446368.780831811</v>
+        <v>7446368.78083181</v>
       </c>
     </row>
     <row r="13">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9388862.7543294</v>
+        <v>9388862.754329402</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9957335.150242776</v>
+        <v>9957335.150242779</v>
       </c>
     </row>
   </sheetData>
@@ -26308,7 +26308,7 @@
         <v>1456380.413613643</v>
       </c>
       <c r="O2" t="n">
-        <v>1327469.058072514</v>
+        <v>1327469.058072515</v>
       </c>
       <c r="P2" t="n">
         <v>1240303.409265538</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>652923.0593271848</v>
+        <v>648158.0030306139</v>
       </c>
       <c r="C4" t="n">
-        <v>651170.216826744</v>
+        <v>646405.1605301732</v>
       </c>
       <c r="D4" t="n">
-        <v>649414.9964860472</v>
+        <v>644649.9401894757</v>
       </c>
       <c r="E4" t="n">
-        <v>570194.3782483711</v>
+        <v>565477.7219742872</v>
       </c>
       <c r="F4" t="n">
-        <v>594468.9940423667</v>
+        <v>589752.3377682829</v>
       </c>
       <c r="G4" t="n">
-        <v>619104.2187528976</v>
+        <v>614387.5624788136</v>
       </c>
       <c r="H4" t="n">
-        <v>617431.9192230618</v>
+        <v>612715.2629489779</v>
       </c>
       <c r="I4" t="n">
-        <v>615757.2851359395</v>
+        <v>611040.6288618557</v>
       </c>
       <c r="J4" t="n">
-        <v>555279.9919275022</v>
+        <v>550731.6711073458</v>
       </c>
       <c r="K4" t="n">
-        <v>553815.2502735605</v>
+        <v>549266.929453404</v>
       </c>
       <c r="L4" t="n">
-        <v>608964.7713905404</v>
+        <v>604395.6223202096</v>
       </c>
       <c r="M4" t="n">
-        <v>610210.2365977673</v>
+        <v>605620.1302626282</v>
       </c>
       <c r="N4" t="n">
-        <v>608495.6307072807</v>
+        <v>603905.5243721416</v>
       </c>
       <c r="O4" t="n">
-        <v>546572.4096548219</v>
+        <v>542024.0888346656</v>
       </c>
       <c r="P4" t="n">
-        <v>505693.2836529539</v>
+        <v>501144.9628327976</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>488269.7890719289</v>
+        <v>493034.8453685003</v>
       </c>
       <c r="C6" t="n">
-        <v>776902.6315723697</v>
+        <v>781667.687868941</v>
       </c>
       <c r="D6" t="n">
-        <v>778657.8519130673</v>
+        <v>783422.9082096383</v>
       </c>
       <c r="E6" t="n">
-        <v>532943.618248912</v>
+        <v>537660.2745229957</v>
       </c>
       <c r="F6" t="n">
-        <v>720788.8006740339</v>
+        <v>725505.4569481178</v>
       </c>
       <c r="G6" t="n">
-        <v>748516.853078138</v>
+        <v>753233.509352222</v>
       </c>
       <c r="H6" t="n">
-        <v>772589.152607974</v>
+        <v>777305.8088820577</v>
       </c>
       <c r="I6" t="n">
-        <v>774263.7866950963</v>
+        <v>778980.4429691798</v>
       </c>
       <c r="J6" t="n">
-        <v>306578.045657781</v>
+        <v>311126.3664779371</v>
       </c>
       <c r="K6" t="n">
-        <v>690858.7873117226</v>
+        <v>695407.1081318794</v>
       </c>
       <c r="L6" t="n">
-        <v>703810.7069058107</v>
+        <v>708379.8559761413</v>
       </c>
       <c r="M6" t="n">
-        <v>774440.0430158762</v>
+        <v>779030.1493510153</v>
       </c>
       <c r="N6" t="n">
-        <v>777754.6489063628</v>
+        <v>782344.755241502</v>
       </c>
       <c r="O6" t="n">
-        <v>628778.792417692</v>
+        <v>633327.1132378494</v>
       </c>
       <c r="P6" t="n">
-        <v>671878.0636125836</v>
+        <v>676426.3844327399</v>
       </c>
     </row>
   </sheetData>
@@ -26990,10 +26990,10 @@
         <v>28</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>-0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27433,28 +27433,28 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>400</v>
-      </c>
-      <c r="C2" t="n">
-        <v>400</v>
-      </c>
-      <c r="D2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E2" t="n">
-        <v>400</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,13 +27481,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>153.4284074428799</v>
       </c>
       <c r="S2" t="n">
-        <v>303.5095671255646</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27557,25 +27557,25 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>342.2743756165773</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>115.3536407070569</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27591,22 +27591,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>384.6131736035182</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -27615,10 +27615,10 @@
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>379.1080474869252</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27645,16 +27645,16 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
         <v>247.4436454301076</v>
@@ -27670,22 +27670,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>303.5095671255644</v>
+        <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>400</v>
+        <v>303.5095671255647</v>
       </c>
       <c r="E5" t="n">
         <v>400</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -27721,7 +27721,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27752,13 +27752,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>193.9840721817119</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27770,7 +27770,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,10 +27797,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>159.4007615079257</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27831,10 +27831,10 @@
         <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>301.045125345529</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
@@ -27846,10 +27846,10 @@
         <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>219.3904442350746</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
         <v>400</v>
@@ -27879,10 +27879,10 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
         <v>150.9583912744579</v>
@@ -27894,7 +27894,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>287.4653528494624</v>
@@ -27907,7 +27907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>400</v>
@@ -27922,10 +27922,10 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>303.5095671255647</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27955,13 +27955,13 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>52.63096829726999</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -27973,10 +27973,10 @@
         <v>400</v>
       </c>
       <c r="X8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -27992,7 +27992,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28043,19 +28043,19 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>289.6034552804142</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>342.2743756165773</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>288.2424963134233</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
         <v>272.7252466480447</v>
@@ -28080,7 +28080,7 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
         <v>400</v>
@@ -28092,7 +28092,7 @@
         <v>400</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>296.1889581192062</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28119,13 +28119,13 @@
         <v>400</v>
       </c>
       <c r="T10" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U10" t="n">
         <v>400</v>
       </c>
-      <c r="U10" t="n">
-        <v>150.9583912744579</v>
-      </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
@@ -28247,13 +28247,13 @@
         <v>225</v>
       </c>
       <c r="J12" t="n">
-        <v>225</v>
+        <v>19.11687125883931</v>
       </c>
       <c r="K12" t="n">
         <v>225</v>
       </c>
       <c r="L12" t="n">
-        <v>19.11687125883935</v>
+        <v>225</v>
       </c>
       <c r="M12" t="n">
         <v>225</v>
@@ -28484,25 +28484,25 @@
         <v>251</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>251</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>251</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
+        <v>166.1982915220774</v>
+      </c>
+      <c r="P15" t="n">
         <v>251</v>
-      </c>
-      <c r="P15" t="n">
-        <v>166.1982915220772</v>
       </c>
       <c r="Q15" t="n">
         <v>251</v>
@@ -28639,7 +28639,7 @@
         <v>279</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>146.6309682972706</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>247.42840744288</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S17" t="n">
         <v>279</v>
@@ -28721,28 +28721,28 @@
         <v>279</v>
       </c>
       <c r="J18" t="n">
-        <v>261.5913251766234</v>
+        <v>279</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>155.670590267103</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>279</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28961,25 +28961,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>155.6705902671029</v>
+      </c>
+      <c r="P21" t="n">
         <v>279</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>261.5913251766235</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
       <c r="Q21" t="n">
-        <v>173.0792650904796</v>
+        <v>279</v>
       </c>
       <c r="R21" t="n">
         <v>279</v>
@@ -29104,7 +29104,7 @@
         <v>279</v>
       </c>
       <c r="F23" t="n">
-        <v>279</v>
+        <v>275.549808614586</v>
       </c>
       <c r="G23" t="n">
         <v>279</v>
@@ -29143,7 +29143,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
-        <v>275.5498086145856</v>
+        <v>279</v>
       </c>
       <c r="T23" t="n">
         <v>279</v>
@@ -29195,25 +29195,25 @@
         <v>279</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>155.6705902671029</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>279</v>
-      </c>
-      <c r="K24" t="n">
-        <v>155.670590267103</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>279</v>
@@ -29429,13 +29429,13 @@
         <v>225</v>
       </c>
       <c r="I27" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J27" t="n">
         <v>225</v>
       </c>
       <c r="K27" t="n">
-        <v>26.99048536749083</v>
+        <v>225</v>
       </c>
       <c r="L27" t="n">
         <v>225</v>
@@ -29450,7 +29450,7 @@
         <v>225</v>
       </c>
       <c r="P27" t="n">
-        <v>225</v>
+        <v>19.11687125883908</v>
       </c>
       <c r="Q27" t="n">
         <v>225</v>
@@ -29666,19 +29666,19 @@
         <v>225</v>
       </c>
       <c r="I30" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J30" t="n">
         <v>225</v>
       </c>
       <c r="K30" t="n">
-        <v>78.91122027701118</v>
+        <v>225</v>
       </c>
       <c r="L30" t="n">
         <v>225</v>
       </c>
       <c r="M30" t="n">
-        <v>225</v>
+        <v>19.11687125883925</v>
       </c>
       <c r="N30" t="n">
         <v>225</v>
@@ -29690,7 +29690,7 @@
         <v>225</v>
       </c>
       <c r="Q30" t="n">
-        <v>173.0792650904796</v>
+        <v>225</v>
       </c>
       <c r="R30" t="n">
         <v>225</v>
@@ -29906,7 +29906,7 @@
         <v>284</v>
       </c>
       <c r="J33" t="n">
-        <v>64.14778647157188</v>
+        <v>284</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -29918,7 +29918,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>284</v>
+        <v>64.14778647157223</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -30143,13 +30143,13 @@
         <v>286</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>27.53866495335923</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -30158,10 +30158,10 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>27.53866495335951</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>286</v>
@@ -30380,16 +30380,16 @@
         <v>286</v>
       </c>
       <c r="J39" t="n">
-        <v>27.53866495335923</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>27.53866495335927</v>
       </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>286</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -30614,13 +30614,13 @@
         <v>224</v>
       </c>
       <c r="I42" t="n">
-        <v>217.1263858913485</v>
+        <v>224</v>
       </c>
       <c r="J42" t="n">
-        <v>49.29504612659585</v>
+        <v>224</v>
       </c>
       <c r="K42" t="n">
-        <v>224</v>
+        <v>42.42143201794437</v>
       </c>
       <c r="L42" t="n">
         <v>224</v>
@@ -30729,7 +30729,7 @@
         <v>224</v>
       </c>
       <c r="U43" t="n">
-        <v>217.4493136045008</v>
+        <v>217.4493136045234</v>
       </c>
       <c r="V43" t="n">
         <v>199.1703102162162</v>
@@ -30860,7 +30860,7 @@
         <v>198</v>
       </c>
       <c r="L45" t="n">
-        <v>119.926429050158</v>
+        <v>198</v>
       </c>
       <c r="M45" t="n">
         <v>198</v>
@@ -30872,7 +30872,7 @@
         <v>198</v>
       </c>
       <c r="P45" t="n">
-        <v>198</v>
+        <v>78.14855155432936</v>
       </c>
       <c r="Q45" t="n">
         <v>198</v>
@@ -30933,7 +30933,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J46" t="n">
-        <v>35.26894883590776</v>
+        <v>109.0765324118717</v>
       </c>
       <c r="K46" t="n">
         <v>198</v>
@@ -34746,10 +34746,10 @@
         <v>815</v>
       </c>
       <c r="K2" t="n">
+        <v>783.0093003026375</v>
+      </c>
+      <c r="L2" t="n">
         <v>815</v>
-      </c>
-      <c r="L2" t="n">
-        <v>783.0093003026025</v>
       </c>
       <c r="M2" t="n">
         <v>815</v>
@@ -34877,22 +34877,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>154.95612715847</v>
+        <v>139.5693007619882</v>
       </c>
       <c r="H4" t="n">
         <v>171.2288738983814</v>
@@ -34901,10 +34901,10 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>90.58727368578215</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34931,16 +34931,16 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -34983,10 +34983,10 @@
         <v>815</v>
       </c>
       <c r="K5" t="n">
-        <v>783.0093003026375</v>
+        <v>815</v>
       </c>
       <c r="L5" t="n">
-        <v>814.9999999999999</v>
+        <v>783.0093003027089</v>
       </c>
       <c r="M5" t="n">
         <v>815</v>
@@ -35117,10 +35117,10 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>15.50890728997348</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
@@ -35132,10 +35132,10 @@
         <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>42.75698861495635</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
         <v>364.7310511640923</v>
@@ -35165,10 +35165,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -35180,7 +35180,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -35220,7 +35220,7 @@
         <v>815</v>
       </c>
       <c r="K8" t="n">
-        <v>783.0093003029165</v>
+        <v>783.0093003026712</v>
       </c>
       <c r="L8" t="n">
         <v>815</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.128695976344588</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -35366,7 +35366,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>171.2288738983814</v>
@@ -35378,7 +35378,7 @@
         <v>364.7310511640923</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>7.668184318063188</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35405,13 +35405,13 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -35454,10 +35454,10 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>395.2617303410664</v>
+        <v>18.61793580165106</v>
       </c>
       <c r="K11" t="n">
-        <v>438.3562054605845</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>815</v>
@@ -35469,7 +35469,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -35533,13 +35533,13 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
-        <v>350.2086062376757</v>
+        <v>144.325477496515</v>
       </c>
       <c r="K12" t="n">
         <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>293.2082466075263</v>
+        <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
         <v>311.9500421645043</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>116.7428182785515</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L14" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,7 +35706,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>536.4810879374849</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -35715,7 +35715,7 @@
         <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
-        <v>5.735449810316382e-14</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -35770,25 +35770,25 @@
         <v>33.87361410865147</v>
       </c>
       <c r="J15" t="n">
-        <v>376.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>442.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>274.091375348687</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M15" t="n">
-        <v>86.95004216450428</v>
+        <v>337.9500421645043</v>
       </c>
       <c r="N15" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>492.4570219027464</v>
+        <v>407.6553134248237</v>
       </c>
       <c r="P15" t="n">
-        <v>279.8642960367304</v>
+        <v>364.6660045146532</v>
       </c>
       <c r="Q15" t="n">
         <v>77.92073490952041</v>
@@ -35934,7 +35934,7 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,13 +35943,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>536.4810879374849</v>
+        <v>164.5104768795733</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36007,16 +36007,16 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J18" t="n">
-        <v>386.7999314142991</v>
+        <v>404.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>191.1038546407913</v>
+        <v>346.7744449078943</v>
       </c>
       <c r="L18" t="n">
         <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>365.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N18" t="n">
         <v>134.6265501086548</v>
@@ -36028,7 +36028,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36165,13 +36165,13 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>814.9999999999999</v>
+        <v>438.3562054605846</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36180,7 +36180,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>116.7428182785516</v>
+        <v>815</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -36247,7 +36247,7 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>470.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L21" t="n">
         <v>274.091375348687</v>
@@ -36259,13 +36259,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>503.0483470793698</v>
+        <v>397.1276121698493</v>
       </c>
       <c r="P21" t="n">
-        <v>113.6660045146532</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36402,13 +36402,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>814.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36417,10 +36417,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="P23" t="n">
-        <v>116.7428182785516</v>
+        <v>438.3562054605844</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36481,16 +36481,16 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J24" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>346.7744449078943</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
         <v>274.091375348687</v>
       </c>
       <c r="M24" t="n">
-        <v>86.95004216450428</v>
+        <v>242.6206324316071</v>
       </c>
       <c r="N24" t="n">
         <v>134.6265501086548</v>
@@ -36499,7 +36499,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P24" t="n">
-        <v>113.6660045146532</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q24" t="n">
         <v>105.9207349095204</v>
@@ -36645,7 +36645,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>753.8135071826036</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36657,10 +36657,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>310.7841182405155</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36715,13 +36715,13 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J27" t="n">
         <v>350.2086062376757</v>
       </c>
       <c r="K27" t="n">
-        <v>218.0943400082821</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
         <v>499.091375348687</v>
@@ -36736,7 +36736,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P27" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734923</v>
       </c>
       <c r="Q27" t="n">
         <v>51.92073490952041</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>149.0841554316853</v>
       </c>
       <c r="K29" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>758</v>
       </c>
       <c r="M29" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>706.0458485815818</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>758</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36952,19 +36952,19 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J30" t="n">
         <v>350.2086062376757</v>
       </c>
       <c r="K30" t="n">
-        <v>270.0150749178025</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L30" t="n">
         <v>499.091375348687</v>
       </c>
       <c r="M30" t="n">
-        <v>311.9500421645043</v>
+        <v>106.0669134233435</v>
       </c>
       <c r="N30" t="n">
         <v>359.6265501086548</v>
@@ -36976,7 +36976,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>51.92073490952041</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37116,7 +37116,7 @@
         <v>758</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -37125,10 +37125,10 @@
         <v>758</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>758</v>
       </c>
       <c r="O32" t="n">
-        <v>655.79641462294</v>
+        <v>614.6715321459594</v>
       </c>
       <c r="P32" t="n">
         <v>758</v>
@@ -37192,7 +37192,7 @@
         <v>66.87361410865147</v>
       </c>
       <c r="J33" t="n">
-        <v>189.3563927092476</v>
+        <v>409.2086062376757</v>
       </c>
       <c r="K33" t="n">
         <v>191.1038546407913</v>
@@ -37204,7 +37204,7 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N33" t="n">
-        <v>418.6265501086548</v>
+        <v>198.774336580227</v>
       </c>
       <c r="O33" t="n">
         <v>241.4570219027464</v>
@@ -37353,19 +37353,19 @@
         <v>758</v>
       </c>
       <c r="K35" t="n">
-        <v>716.8751175230996</v>
+        <v>758</v>
       </c>
       <c r="L35" t="n">
-        <v>551.7865359278883</v>
+        <v>758</v>
       </c>
       <c r="M35" t="n">
         <v>758</v>
       </c>
       <c r="N35" t="n">
-        <v>758.0000000000006</v>
+        <v>758</v>
       </c>
       <c r="O35" t="n">
-        <v>758</v>
+        <v>510.6616534510043</v>
       </c>
       <c r="P35" t="n">
         <v>758</v>
@@ -37429,13 +37429,13 @@
         <v>68.87361410865147</v>
       </c>
       <c r="J36" t="n">
-        <v>125.2086062376757</v>
+        <v>152.7472711910349</v>
       </c>
       <c r="K36" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L36" t="n">
-        <v>274.091375348687</v>
+        <v>560.0913753486871</v>
       </c>
       <c r="M36" t="n">
         <v>86.95004216450428</v>
@@ -37444,10 +37444,10 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O36" t="n">
-        <v>527.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P36" t="n">
-        <v>141.2046694680127</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q36" t="n">
         <v>112.9207349095204</v>
@@ -37590,10 +37590,10 @@
         <v>758</v>
       </c>
       <c r="K38" t="n">
-        <v>758</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L38" t="n">
-        <v>510.6616534510117</v>
+        <v>551.7865359278771</v>
       </c>
       <c r="M38" t="n">
         <v>758</v>
@@ -37666,16 +37666,16 @@
         <v>68.87361410865147</v>
       </c>
       <c r="J39" t="n">
-        <v>152.7472711910349</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K39" t="n">
-        <v>191.1038546407913</v>
+        <v>218.6425195941506</v>
       </c>
       <c r="L39" t="n">
-        <v>560.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M39" t="n">
-        <v>86.95004216450428</v>
+        <v>372.9500421645043</v>
       </c>
       <c r="N39" t="n">
         <v>134.6265501086548</v>
@@ -37824,13 +37824,13 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>349.9503550467658</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>758</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
@@ -37839,13 +37839,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>758.000000000004</v>
+        <v>310.7841182405155</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37900,13 +37900,13 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>6.873614108651466</v>
       </c>
       <c r="J42" t="n">
-        <v>174.5036523642715</v>
+        <v>349.2086062376757</v>
       </c>
       <c r="K42" t="n">
-        <v>415.1038546407913</v>
+        <v>233.5252866587357</v>
       </c>
       <c r="L42" t="n">
         <v>498.091375348687</v>
@@ -38015,7 +38015,7 @@
         <v>13.97543349374229</v>
       </c>
       <c r="U43" t="n">
-        <v>66.49092233004288</v>
+        <v>66.49092233006544</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38146,7 +38146,7 @@
         <v>389.1038546407913</v>
       </c>
       <c r="L45" t="n">
-        <v>394.0178043988449</v>
+        <v>472.091375348687</v>
       </c>
       <c r="M45" t="n">
         <v>284.9500421645043</v>
@@ -38158,7 +38158,7 @@
         <v>439.4570219027464</v>
       </c>
       <c r="P45" t="n">
-        <v>311.6660045146532</v>
+        <v>191.8145560689825</v>
       </c>
       <c r="Q45" t="n">
         <v>24.92073490952041</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>73.8075835759639</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
